--- a/research/traditional_assets/database/data/hong_kong/hong_kong_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_paper_forest_products.xlsx
@@ -2049,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2186,22 +2186,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0799307660262332</v>
+        <v>0.07983645526228991</v>
       </c>
       <c r="C2">
-        <v>4130.217700509476</v>
+        <v>4099.506172854021</v>
       </c>
       <c r="D2">
-        <v>3906.517700509476</v>
+        <v>3917.342172854021</v>
       </c>
       <c r="E2">
-        <v>-2821</v>
+        <v>-2779.464</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>41.536</v>
       </c>
       <c r="G2">
         <v>223.7</v>
@@ -2222,28 +2222,28 @@
         <v>220.475</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.0892608</v>
       </c>
       <c r="N2">
-        <v>220.475</v>
+        <v>218.3857392</v>
       </c>
       <c r="O2">
-        <v>36.378375</v>
+        <v>36.033646968</v>
       </c>
       <c r="P2">
-        <v>184.096625</v>
+        <v>182.352092232</v>
       </c>
       <c r="Q2">
-        <v>200.996625</v>
+        <v>199.252092232</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0799307660262332</v>
+        <v>0.08021863662857567</v>
       </c>
       <c r="T2">
-        <v>0.6652721574126822</v>
+        <v>0.6708832912656074</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>105.527754122415</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2268,22 +2268,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07983645526228991</v>
+        <v>0.07974214449834661</v>
       </c>
       <c r="C3">
-        <v>4099.506172854021</v>
+        <v>4068.854798395791</v>
       </c>
       <c r="D3">
-        <v>3917.342172854021</v>
+        <v>3928.226798395791</v>
       </c>
       <c r="E3">
-        <v>-2779.464</v>
+        <v>-2737.928</v>
       </c>
       <c r="F3">
-        <v>41.536</v>
+        <v>83.072</v>
       </c>
       <c r="G3">
         <v>223.7</v>
@@ -2304,28 +2304,28 @@
         <v>220.475</v>
       </c>
       <c r="M3">
-        <v>2.0892608</v>
+        <v>4.1785216</v>
       </c>
       <c r="N3">
-        <v>218.3857392</v>
+        <v>216.2964784</v>
       </c>
       <c r="O3">
-        <v>36.033646968</v>
+        <v>35.688918936</v>
       </c>
       <c r="P3">
-        <v>182.352092232</v>
+        <v>180.607559464</v>
       </c>
       <c r="Q3">
-        <v>199.252092232</v>
+        <v>197.507559464</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08021863662857567</v>
+        <v>0.08051238214117001</v>
       </c>
       <c r="T3">
-        <v>0.6708832912656074</v>
+        <v>0.6766089380543064</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>105.527754122415</v>
+        <v>52.76387706120748</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2350,22 +2350,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07974214449834661</v>
+        <v>0.07964783373440334</v>
       </c>
       <c r="C4">
-        <v>4068.854798395791</v>
+        <v>4038.264079952247</v>
       </c>
       <c r="D4">
-        <v>3928.226798395791</v>
+        <v>3939.172079952247</v>
       </c>
       <c r="E4">
-        <v>-2737.928</v>
+        <v>-2696.392</v>
       </c>
       <c r="F4">
-        <v>83.072</v>
+        <v>124.608</v>
       </c>
       <c r="G4">
         <v>223.7</v>
@@ -2386,28 +2386,28 @@
         <v>220.475</v>
       </c>
       <c r="M4">
-        <v>4.1785216</v>
+        <v>6.2677824</v>
       </c>
       <c r="N4">
-        <v>216.2964784</v>
+        <v>214.2072176</v>
       </c>
       <c r="O4">
-        <v>35.688918936</v>
+        <v>35.344190904</v>
       </c>
       <c r="P4">
-        <v>180.607559464</v>
+        <v>178.863026696</v>
       </c>
       <c r="Q4">
-        <v>197.507559464</v>
+        <v>195.763026696</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08051238214117001</v>
+        <v>0.08081218426227149</v>
       </c>
       <c r="T4">
-        <v>0.6766089380543064</v>
+        <v>0.6824526394159686</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>52.76387706120748</v>
+        <v>35.17591804080499</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2432,22 +2432,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07964783373440334</v>
+        <v>0.07955352297046005</v>
       </c>
       <c r="C5">
-        <v>4038.264079952247</v>
+        <v>4007.73452596055</v>
       </c>
       <c r="D5">
-        <v>3939.172079952247</v>
+        <v>3950.17852596055</v>
       </c>
       <c r="E5">
-        <v>-2696.392</v>
+        <v>-2654.856</v>
       </c>
       <c r="F5">
-        <v>124.608</v>
+        <v>166.144</v>
       </c>
       <c r="G5">
         <v>223.7</v>
@@ -2468,28 +2468,28 @@
         <v>220.475</v>
       </c>
       <c r="M5">
-        <v>6.2677824</v>
+        <v>8.3570432</v>
       </c>
       <c r="N5">
-        <v>214.2072176</v>
+        <v>212.1179568</v>
       </c>
       <c r="O5">
-        <v>35.344190904</v>
+        <v>34.999462872</v>
       </c>
       <c r="P5">
-        <v>178.863026696</v>
+        <v>177.118493928</v>
       </c>
       <c r="Q5">
-        <v>195.763026696</v>
+        <v>194.018493928</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08081218426227149</v>
+        <v>0.08111823226089589</v>
       </c>
       <c r="T5">
-        <v>0.6824526394159686</v>
+        <v>0.6884180845559985</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>35.17591804080499</v>
+        <v>26.38193853060374</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2514,22 +2514,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07955352297046005</v>
+        <v>0.07945921220651676</v>
       </c>
       <c r="C6">
-        <v>4007.73452596055</v>
+        <v>3977.266650556276</v>
       </c>
       <c r="D6">
-        <v>3950.17852596055</v>
+        <v>3961.246650556276</v>
       </c>
       <c r="E6">
-        <v>-2654.856</v>
+        <v>-2613.32</v>
       </c>
       <c r="F6">
-        <v>166.144</v>
+        <v>207.68</v>
       </c>
       <c r="G6">
         <v>223.7</v>
@@ -2550,28 +2550,28 @@
         <v>220.475</v>
       </c>
       <c r="M6">
-        <v>8.3570432</v>
+        <v>10.446304</v>
       </c>
       <c r="N6">
-        <v>212.1179568</v>
+        <v>210.028696</v>
       </c>
       <c r="O6">
-        <v>34.999462872</v>
+        <v>34.65473484</v>
       </c>
       <c r="P6">
-        <v>177.118493928</v>
+        <v>175.37396116</v>
       </c>
       <c r="Q6">
-        <v>194.018493928</v>
+        <v>192.27396116</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08111823226089589</v>
+        <v>0.0814307233752808</v>
       </c>
       <c r="T6">
-        <v>0.6884180845559985</v>
+        <v>0.6945091180147659</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>26.38193853060374</v>
+        <v>21.10555082448299</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2596,22 +2596,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07945921220651676</v>
+        <v>0.07936490144257348</v>
       </c>
       <c r="C7">
-        <v>3977.266650556276</v>
+        <v>3946.860973653483</v>
       </c>
       <c r="D7">
-        <v>3961.246650556276</v>
+        <v>3972.376973653483</v>
       </c>
       <c r="E7">
-        <v>-2613.32</v>
+        <v>-2571.784</v>
       </c>
       <c r="F7">
-        <v>207.68</v>
+        <v>249.216</v>
       </c>
       <c r="G7">
         <v>223.7</v>
@@ -2632,28 +2632,28 @@
         <v>220.475</v>
       </c>
       <c r="M7">
-        <v>10.446304</v>
+        <v>12.5355648</v>
       </c>
       <c r="N7">
-        <v>210.028696</v>
+        <v>207.9394352</v>
       </c>
       <c r="O7">
-        <v>34.65473484</v>
+        <v>34.310006808</v>
       </c>
       <c r="P7">
-        <v>175.37396116</v>
+        <v>173.629428392</v>
       </c>
       <c r="Q7">
-        <v>192.27396116</v>
+        <v>190.529428392</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0814307233752808</v>
+        <v>0.0817498632367803</v>
       </c>
       <c r="T7">
-        <v>0.6945091180147659</v>
+        <v>0.7007297479301029</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.10555082448299</v>
+        <v>17.58795902040249</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2678,22 +2678,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07936490144257347</v>
+        <v>0.0792705906786302</v>
       </c>
       <c r="C8">
-        <v>3946.860973653484</v>
+        <v>3916.518021026117</v>
       </c>
       <c r="D8">
-        <v>3972.376973653484</v>
+        <v>3983.570021026117</v>
       </c>
       <c r="E8">
-        <v>-2571.784</v>
+        <v>-2530.248</v>
       </c>
       <c r="F8">
-        <v>249.216</v>
+        <v>290.752</v>
       </c>
       <c r="G8">
         <v>223.7</v>
@@ -2714,28 +2714,28 @@
         <v>220.475</v>
       </c>
       <c r="M8">
-        <v>12.5355648</v>
+        <v>14.6248256</v>
       </c>
       <c r="N8">
-        <v>207.9394352</v>
+        <v>205.8501744</v>
       </c>
       <c r="O8">
-        <v>34.310006808</v>
+        <v>33.965278776</v>
       </c>
       <c r="P8">
-        <v>173.629428392</v>
+        <v>171.884895624</v>
       </c>
       <c r="Q8">
-        <v>190.529428392</v>
+        <v>188.784895624</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0817498632367803</v>
+        <v>0.08207586632110773</v>
       </c>
       <c r="T8">
-        <v>0.7007297479301029</v>
+        <v>0.7070841548328664</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.58795902040249</v>
+        <v>15.07539344605928</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2760,22 +2760,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0792705906786302</v>
+        <v>0.0791762799146869</v>
       </c>
       <c r="C9">
-        <v>3916.518021026117</v>
+        <v>3886.238324390809</v>
       </c>
       <c r="D9">
-        <v>3983.570021026117</v>
+        <v>3994.826324390809</v>
       </c>
       <c r="E9">
-        <v>-2530.248</v>
+        <v>-2488.712</v>
       </c>
       <c r="F9">
-        <v>290.7520000000001</v>
+        <v>332.288</v>
       </c>
       <c r="G9">
         <v>223.7</v>
@@ -2796,28 +2796,28 @@
         <v>220.475</v>
       </c>
       <c r="M9">
-        <v>14.6248256</v>
+        <v>16.7140864</v>
       </c>
       <c r="N9">
-        <v>205.8501744</v>
+        <v>203.7609136</v>
       </c>
       <c r="O9">
-        <v>33.965278776</v>
+        <v>33.620550744</v>
       </c>
       <c r="P9">
-        <v>171.884895624</v>
+        <v>170.140362856</v>
       </c>
       <c r="Q9">
-        <v>188.784895624</v>
+        <v>187.040362856</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08207586632110775</v>
+        <v>0.0824089564290075</v>
       </c>
       <c r="T9">
-        <v>0.7070841548328665</v>
+        <v>0.7135767010161247</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.07539344605928</v>
+        <v>13.19096926530187</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2842,22 +2842,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0791762799146869</v>
+        <v>0.07919469415074362</v>
       </c>
       <c r="C10">
-        <v>3886.238324390809</v>
+        <v>3842.499529102106</v>
       </c>
       <c r="D10">
-        <v>3994.826324390809</v>
+        <v>3992.623529102106</v>
       </c>
       <c r="E10">
-        <v>-2488.712</v>
+        <v>-2447.176</v>
       </c>
       <c r="F10">
-        <v>332.288</v>
+        <v>373.824</v>
       </c>
       <c r="G10">
         <v>223.7</v>
@@ -2878,45 +2878,45 @@
         <v>220.475</v>
       </c>
       <c r="M10">
-        <v>16.7140864</v>
+        <v>19.3640832</v>
       </c>
       <c r="N10">
-        <v>203.7609136</v>
+        <v>201.1109168</v>
       </c>
       <c r="O10">
-        <v>33.620550744</v>
+        <v>33.183301272</v>
       </c>
       <c r="P10">
-        <v>170.140362856</v>
+        <v>167.927615528</v>
       </c>
       <c r="Q10">
-        <v>187.040362856</v>
+        <v>184.827615528</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0824089564290075</v>
+        <v>0.08274936719861936</v>
       </c>
       <c r="T10">
-        <v>0.7135767010161247</v>
+        <v>0.720211940522092</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.165</v>
       </c>
       <c r="W10">
-        <v>0.0420005</v>
+        <v>0.043253</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.19096926530187</v>
+        <v>11.3857701251769</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2924,22 +2924,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07919469415074362</v>
+        <v>0.07911290838680035</v>
       </c>
       <c r="C11">
-        <v>3842.499529102106</v>
+        <v>3810.765728347935</v>
       </c>
       <c r="D11">
-        <v>3992.623529102106</v>
+        <v>4002.425728347936</v>
       </c>
       <c r="E11">
-        <v>-2447.176</v>
+        <v>-2405.64</v>
       </c>
       <c r="F11">
-        <v>373.824</v>
+        <v>415.36</v>
       </c>
       <c r="G11">
         <v>223.7</v>
@@ -2960,28 +2960,28 @@
         <v>220.475</v>
       </c>
       <c r="M11">
-        <v>19.3640832</v>
+        <v>21.515648</v>
       </c>
       <c r="N11">
-        <v>201.1109168</v>
+        <v>198.959352</v>
       </c>
       <c r="O11">
-        <v>33.183301272</v>
+        <v>32.82829308</v>
       </c>
       <c r="P11">
-        <v>167.927615528</v>
+        <v>166.13105892</v>
       </c>
       <c r="Q11">
-        <v>184.827615528</v>
+        <v>183.03105892</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08274936719861936</v>
+        <v>0.08309734265200039</v>
       </c>
       <c r="T11">
-        <v>0.720211940522092</v>
+        <v>0.7269946297948588</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.3857701251769</v>
+        <v>10.24719311265921</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -3006,22 +3006,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07911290838680035</v>
+        <v>0.07918726762285706</v>
       </c>
       <c r="C12">
-        <v>3810.765728347935</v>
+        <v>3760.315632025483</v>
       </c>
       <c r="D12">
-        <v>4002.425728347936</v>
+        <v>3993.511632025482</v>
       </c>
       <c r="E12">
-        <v>-2405.64</v>
+        <v>-2364.104</v>
       </c>
       <c r="F12">
-        <v>415.3600000000001</v>
+        <v>456.896</v>
       </c>
       <c r="G12">
         <v>223.7</v>
@@ -3042,45 +3042,45 @@
         <v>220.475</v>
       </c>
       <c r="M12">
-        <v>21.515648</v>
+        <v>24.443936</v>
       </c>
       <c r="N12">
-        <v>198.959352</v>
+        <v>196.031064</v>
       </c>
       <c r="O12">
-        <v>32.82829308</v>
+        <v>32.34512556</v>
       </c>
       <c r="P12">
-        <v>166.13105892</v>
+        <v>163.68593844</v>
       </c>
       <c r="Q12">
-        <v>183.03105892</v>
+        <v>180.58593844</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08309734265200039</v>
+        <v>0.08345313777849107</v>
       </c>
       <c r="T12">
-        <v>0.7269946297948588</v>
+        <v>0.7339297390512831</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.165</v>
       </c>
       <c r="W12">
-        <v>0.043253</v>
+        <v>0.0446725</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.24719311265921</v>
+        <v>9.019619426265884</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -3088,22 +3088,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07918726762285706</v>
+        <v>0.07911967685891376</v>
       </c>
       <c r="C13">
-        <v>3760.315632025483</v>
+        <v>3726.880686041342</v>
       </c>
       <c r="D13">
-        <v>3993.511632025482</v>
+        <v>4001.612686041342</v>
       </c>
       <c r="E13">
-        <v>-2364.104</v>
+        <v>-2322.568</v>
       </c>
       <c r="F13">
-        <v>456.896</v>
+        <v>498.432</v>
       </c>
       <c r="G13">
         <v>223.7</v>
@@ -3124,28 +3124,28 @@
         <v>220.475</v>
       </c>
       <c r="M13">
-        <v>24.443936</v>
+        <v>26.666112</v>
       </c>
       <c r="N13">
-        <v>196.031064</v>
+        <v>193.808888</v>
       </c>
       <c r="O13">
-        <v>32.34512556</v>
+        <v>31.97846652</v>
       </c>
       <c r="P13">
-        <v>163.68593844</v>
+        <v>161.83042148</v>
       </c>
       <c r="Q13">
-        <v>180.58593844</v>
+        <v>178.73042148</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08345313777849107</v>
+        <v>0.08381701915785655</v>
       </c>
       <c r="T13">
-        <v>0.7339297390512831</v>
+        <v>0.7410224644271717</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.019619426265884</v>
+        <v>8.26798447407706</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -3170,22 +3170,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07911967685891376</v>
+        <v>0.0790520860949705</v>
       </c>
       <c r="C14">
-        <v>3726.880686041342</v>
+        <v>3693.478673716043</v>
       </c>
       <c r="D14">
-        <v>4001.612686041342</v>
+        <v>4009.746673716043</v>
       </c>
       <c r="E14">
-        <v>-2322.568</v>
+        <v>-2281.032</v>
       </c>
       <c r="F14">
-        <v>498.432</v>
+        <v>539.9680000000001</v>
       </c>
       <c r="G14">
         <v>223.7</v>
@@ -3206,28 +3206,28 @@
         <v>220.475</v>
       </c>
       <c r="M14">
-        <v>26.666112</v>
+        <v>28.888288</v>
       </c>
       <c r="N14">
-        <v>193.808888</v>
+        <v>191.586712</v>
       </c>
       <c r="O14">
-        <v>31.97846652</v>
+        <v>31.61180748</v>
       </c>
       <c r="P14">
-        <v>161.83042148</v>
+        <v>159.97490452</v>
       </c>
       <c r="Q14">
-        <v>178.73042148</v>
+        <v>176.87490452</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08381701915785655</v>
+        <v>0.08418926562640286</v>
       </c>
       <c r="T14">
-        <v>0.7410224644271717</v>
+        <v>0.7482782409611266</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.26798447407706</v>
+        <v>7.631985668378824</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -3252,22 +3252,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0790520860949705</v>
+        <v>0.07907801533102719</v>
       </c>
       <c r="C15">
-        <v>3693.478673716043</v>
+        <v>3648.818398815749</v>
       </c>
       <c r="D15">
-        <v>4009.746673716043</v>
+        <v>4006.622398815749</v>
       </c>
       <c r="E15">
-        <v>-2281.032</v>
+        <v>-2239.496</v>
       </c>
       <c r="F15">
-        <v>539.9680000000001</v>
+        <v>581.5040000000001</v>
       </c>
       <c r="G15">
         <v>223.7</v>
@@ -3288,45 +3288,45 @@
         <v>220.475</v>
       </c>
       <c r="M15">
-        <v>28.888288</v>
+        <v>31.57566720000001</v>
       </c>
       <c r="N15">
-        <v>191.586712</v>
+        <v>188.8993328</v>
       </c>
       <c r="O15">
-        <v>31.61180748</v>
+        <v>31.168389912</v>
       </c>
       <c r="P15">
-        <v>159.97490452</v>
+        <v>157.730942888</v>
       </c>
       <c r="Q15">
-        <v>176.87490452</v>
+        <v>174.630942888</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08418926562640286</v>
+        <v>0.08457016898956651</v>
       </c>
       <c r="T15">
-        <v>0.7482782409611266</v>
+        <v>0.7557027564842433</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.165</v>
       </c>
       <c r="W15">
-        <v>0.0446725</v>
+        <v>0.0453405</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>7.631985668378824</v>
+        <v>6.982433612677547</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3334,22 +3334,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07907801533102719</v>
+        <v>0.07901710456708393</v>
       </c>
       <c r="C16">
-        <v>3648.818398815749</v>
+        <v>3614.629409770639</v>
       </c>
       <c r="D16">
-        <v>4006.622398815749</v>
+        <v>4013.969409770639</v>
       </c>
       <c r="E16">
-        <v>-2239.496</v>
+        <v>-2197.96</v>
       </c>
       <c r="F16">
-        <v>581.5040000000001</v>
+        <v>623.0400000000002</v>
       </c>
       <c r="G16">
         <v>223.7</v>
@@ -3370,28 +3370,28 @@
         <v>220.475</v>
       </c>
       <c r="M16">
-        <v>31.57566720000001</v>
+        <v>33.83107200000001</v>
       </c>
       <c r="N16">
-        <v>188.8993328</v>
+        <v>186.643928</v>
       </c>
       <c r="O16">
-        <v>31.168389912</v>
+        <v>30.79624812</v>
       </c>
       <c r="P16">
-        <v>157.730942888</v>
+        <v>155.84767988</v>
       </c>
       <c r="Q16">
-        <v>174.630942888</v>
+        <v>172.74767988</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08457016898956651</v>
+        <v>0.08496003478480461</v>
       </c>
       <c r="T16">
-        <v>0.7557027564842433</v>
+        <v>0.7633019664902569</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.982433612677547</v>
+        <v>6.516938038499044</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3416,22 +3416,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07901710456708393</v>
+        <v>0.07908979380314063</v>
       </c>
       <c r="C17">
-        <v>3614.629409770639</v>
+        <v>3564.328790449876</v>
       </c>
       <c r="D17">
-        <v>4013.969409770639</v>
+        <v>4005.204790449876</v>
       </c>
       <c r="E17">
-        <v>-2197.96</v>
+        <v>-2156.424</v>
       </c>
       <c r="F17">
-        <v>623.0400000000001</v>
+        <v>664.576</v>
       </c>
       <c r="G17">
         <v>223.7</v>
@@ -3452,45 +3452,45 @@
         <v>220.475</v>
       </c>
       <c r="M17">
-        <v>33.83107200000001</v>
+        <v>36.7510528</v>
       </c>
       <c r="N17">
-        <v>186.643928</v>
+        <v>183.7239472</v>
       </c>
       <c r="O17">
-        <v>30.79624812</v>
+        <v>30.314451288</v>
       </c>
       <c r="P17">
-        <v>155.84767988</v>
+        <v>153.409495912</v>
       </c>
       <c r="Q17">
-        <v>172.74767988</v>
+        <v>170.309495912</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08496003478480461</v>
+        <v>0.08535918309897694</v>
       </c>
       <c r="T17">
-        <v>0.7633019664902569</v>
+        <v>0.7710821100678422</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.165</v>
       </c>
       <c r="W17">
-        <v>0.0453405</v>
+        <v>0.0461755</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.516938038499045</v>
+        <v>5.999147866588464</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3498,22 +3498,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07908979380314063</v>
+        <v>0.07903723303919734</v>
       </c>
       <c r="C18">
-        <v>3564.328790449876</v>
+        <v>3529.126549438993</v>
       </c>
       <c r="D18">
-        <v>4005.204790449876</v>
+        <v>4011.538549438993</v>
       </c>
       <c r="E18">
-        <v>-2156.424</v>
+        <v>-2114.888</v>
       </c>
       <c r="F18">
-        <v>664.576</v>
+        <v>706.1120000000001</v>
       </c>
       <c r="G18">
         <v>223.7</v>
@@ -3534,28 +3534,28 @@
         <v>220.475</v>
       </c>
       <c r="M18">
-        <v>36.7510528</v>
+        <v>39.04799360000001</v>
       </c>
       <c r="N18">
-        <v>183.7239472</v>
+        <v>181.4270064</v>
       </c>
       <c r="O18">
-        <v>30.314451288</v>
+        <v>29.935456056</v>
       </c>
       <c r="P18">
-        <v>153.409495912</v>
+        <v>151.491550344</v>
       </c>
       <c r="Q18">
-        <v>170.309495912</v>
+        <v>168.391550344</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08535918309897694</v>
+        <v>0.08576794944481608</v>
       </c>
       <c r="T18">
-        <v>0.7710821100678422</v>
+        <v>0.7790497269846464</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.999147866588464</v>
+        <v>5.646256815612671</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3580,22 +3580,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07903723303919734</v>
+        <v>0.07898467227525405</v>
       </c>
       <c r="C19">
-        <v>3529.126549438993</v>
+        <v>3493.944372342457</v>
       </c>
       <c r="D19">
-        <v>4011.538549438993</v>
+        <v>4017.892372342458</v>
       </c>
       <c r="E19">
-        <v>-2114.888</v>
+        <v>-2073.352</v>
       </c>
       <c r="F19">
-        <v>706.1120000000001</v>
+        <v>747.6480000000001</v>
       </c>
       <c r="G19">
         <v>223.7</v>
@@ -3616,28 +3616,28 @@
         <v>220.475</v>
       </c>
       <c r="M19">
-        <v>39.04799360000001</v>
+        <v>41.34493440000001</v>
       </c>
       <c r="N19">
-        <v>181.4270064</v>
+        <v>179.1300656</v>
       </c>
       <c r="O19">
-        <v>29.935456056</v>
+        <v>29.556460824</v>
       </c>
       <c r="P19">
-        <v>151.491550344</v>
+        <v>149.573604776</v>
       </c>
       <c r="Q19">
-        <v>168.391550344</v>
+        <v>166.473604776</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08576794944481608</v>
+        <v>0.08618668570152935</v>
       </c>
       <c r="T19">
-        <v>0.7790497269846464</v>
+        <v>0.7872116760213727</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.646256815612671</v>
+        <v>5.332575881411967</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3662,22 +3662,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07898467227525408</v>
+        <v>0.07893211151131078</v>
       </c>
       <c r="C20">
-        <v>3493.944372342454</v>
+        <v>3458.782354648415</v>
       </c>
       <c r="D20">
-        <v>4017.892372342454</v>
+        <v>4024.266354648415</v>
       </c>
       <c r="E20">
-        <v>-2073.352</v>
+        <v>-2031.816</v>
       </c>
       <c r="F20">
-        <v>747.648</v>
+        <v>789.1840000000001</v>
       </c>
       <c r="G20">
         <v>223.7</v>
@@ -3698,28 +3698,28 @@
         <v>220.475</v>
       </c>
       <c r="M20">
-        <v>41.3449344</v>
+        <v>43.64187520000001</v>
       </c>
       <c r="N20">
-        <v>179.1300656</v>
+        <v>176.8331248</v>
       </c>
       <c r="O20">
-        <v>29.556460824</v>
+        <v>29.177465592</v>
       </c>
       <c r="P20">
-        <v>149.573604776</v>
+        <v>147.655659208</v>
       </c>
       <c r="Q20">
-        <v>166.473604776</v>
+        <v>164.555659208</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08618668570152935</v>
+        <v>0.08661576112507503</v>
       </c>
       <c r="T20">
-        <v>0.7872116760213727</v>
+        <v>0.7955751546639439</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3736,7 +3736,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.332575881411968</v>
+        <v>5.0519139929166</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3744,22 +3744,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07893211151131078</v>
+        <v>0.07887955074736749</v>
       </c>
       <c r="C21">
-        <v>3458.782354648415</v>
+        <v>3423.640592451915</v>
       </c>
       <c r="D21">
-        <v>4024.266354648415</v>
+        <v>4030.660592451915</v>
       </c>
       <c r="E21">
-        <v>-2031.816</v>
+        <v>-1990.28</v>
       </c>
       <c r="F21">
-        <v>789.1840000000001</v>
+        <v>830.7200000000001</v>
       </c>
       <c r="G21">
         <v>223.7</v>
@@ -3780,28 +3780,28 @@
         <v>220.475</v>
       </c>
       <c r="M21">
-        <v>43.64187520000001</v>
+        <v>45.93881600000001</v>
       </c>
       <c r="N21">
-        <v>176.8331248</v>
+        <v>174.536184</v>
       </c>
       <c r="O21">
-        <v>29.177465592</v>
+        <v>28.79847036</v>
       </c>
       <c r="P21">
-        <v>147.655659208</v>
+        <v>145.73771364</v>
       </c>
       <c r="Q21">
-        <v>164.555659208</v>
+        <v>162.63771364</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08661576112507503</v>
+        <v>0.08705556343420937</v>
       </c>
       <c r="T21">
-        <v>0.7955751546639439</v>
+        <v>0.8041477202725796</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.0519139929166</v>
+        <v>4.799318293270771</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3826,22 +3826,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07887955074736749</v>
+        <v>0.07882698998342422</v>
       </c>
       <c r="C22">
-        <v>3423.640592451915</v>
+        <v>3388.519182459713</v>
       </c>
       <c r="D22">
-        <v>4030.660592451915</v>
+        <v>4037.075182459713</v>
       </c>
       <c r="E22">
-        <v>-1990.28</v>
+        <v>-1948.744</v>
       </c>
       <c r="F22">
-        <v>830.7200000000001</v>
+        <v>872.2560000000002</v>
       </c>
       <c r="G22">
         <v>223.7</v>
@@ -3862,28 +3862,28 @@
         <v>220.475</v>
       </c>
       <c r="M22">
-        <v>45.93881600000001</v>
+        <v>48.23575680000001</v>
       </c>
       <c r="N22">
-        <v>174.536184</v>
+        <v>172.2392432</v>
       </c>
       <c r="O22">
-        <v>28.79847036</v>
+        <v>28.419475128</v>
       </c>
       <c r="P22">
-        <v>145.73771364</v>
+        <v>143.819768072</v>
       </c>
       <c r="Q22">
-        <v>162.63771364</v>
+        <v>160.719768072</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08705556343420937</v>
+        <v>0.08750649997901798</v>
       </c>
       <c r="T22">
-        <v>0.8041477202725796</v>
+        <v>0.812937312858649</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3900,7 +3900,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.799318293270771</v>
+        <v>4.570779326924542</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3908,22 +3908,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07882698998342422</v>
+        <v>0.07923367921948093</v>
       </c>
       <c r="C23">
-        <v>3388.519182459713</v>
+        <v>3297.875963027477</v>
       </c>
       <c r="D23">
-        <v>4037.075182459713</v>
+        <v>3987.967963027476</v>
       </c>
       <c r="E23">
-        <v>-1948.744</v>
+        <v>-1907.208</v>
       </c>
       <c r="F23">
-        <v>872.2560000000001</v>
+        <v>913.792</v>
       </c>
       <c r="G23">
         <v>223.7</v>
@@ -3944,45 +3944,45 @@
         <v>220.475</v>
       </c>
       <c r="M23">
-        <v>48.2357568</v>
+        <v>52.81717760000001</v>
       </c>
       <c r="N23">
-        <v>172.2392432</v>
+        <v>167.6578224</v>
       </c>
       <c r="O23">
-        <v>28.419475128</v>
+        <v>27.663540696</v>
       </c>
       <c r="P23">
-        <v>143.819768072</v>
+        <v>139.994281704</v>
       </c>
       <c r="Q23">
-        <v>160.719768072</v>
+        <v>156.894281704</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08750649997901798</v>
+        <v>0.08796899899933452</v>
       </c>
       <c r="T23">
-        <v>0.812937312858649</v>
+        <v>0.8219522796135921</v>
       </c>
       <c r="U23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.165</v>
       </c>
       <c r="W23">
-        <v>0.0461755</v>
+        <v>0.048263</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.570779326924543</v>
+        <v>4.174304838280491</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3990,22 +3990,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07923367921948093</v>
+        <v>0.07987416845553764</v>
       </c>
       <c r="C24">
-        <v>3297.875963027477</v>
+        <v>3181.378469619617</v>
       </c>
       <c r="D24">
-        <v>3987.967963027476</v>
+        <v>3913.006469619616</v>
       </c>
       <c r="E24">
-        <v>-1907.208</v>
+        <v>-1865.672</v>
       </c>
       <c r="F24">
-        <v>913.792</v>
+        <v>955.3280000000001</v>
       </c>
       <c r="G24">
         <v>223.7</v>
@@ -4026,45 +4026,45 @@
         <v>220.475</v>
       </c>
       <c r="M24">
-        <v>52.81717760000001</v>
+        <v>58.5616064</v>
       </c>
       <c r="N24">
-        <v>167.6578224</v>
+        <v>161.9133936</v>
       </c>
       <c r="O24">
-        <v>27.663540696</v>
+        <v>26.715709944</v>
       </c>
       <c r="P24">
-        <v>139.994281704</v>
+        <v>135.197683656</v>
       </c>
       <c r="Q24">
-        <v>156.894281704</v>
+        <v>152.097683656</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08796899899933452</v>
+        <v>0.08844351098121771</v>
       </c>
       <c r="T24">
-        <v>0.8219522796135921</v>
+        <v>0.831201401349183</v>
       </c>
       <c r="U24">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V24">
         <v>0.165</v>
       </c>
       <c r="W24">
-        <v>0.048263</v>
+        <v>0.05118549999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.174304838280491</v>
+        <v>3.764838663988562</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -4072,22 +4072,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07987416845553764</v>
+        <v>0.07987170769159435</v>
       </c>
       <c r="C25">
-        <v>3181.378469619617</v>
+        <v>3140.125079030259</v>
       </c>
       <c r="D25">
-        <v>3913.006469619616</v>
+        <v>3913.289079030259</v>
       </c>
       <c r="E25">
-        <v>-1865.672</v>
+        <v>-1824.136</v>
       </c>
       <c r="F25">
-        <v>955.3280000000001</v>
+        <v>996.8640000000001</v>
       </c>
       <c r="G25">
         <v>223.7</v>
@@ -4108,28 +4108,28 @@
         <v>220.475</v>
       </c>
       <c r="M25">
-        <v>58.5616064</v>
+        <v>61.10776320000001</v>
       </c>
       <c r="N25">
-        <v>161.9133936</v>
+        <v>159.3672368</v>
       </c>
       <c r="O25">
-        <v>26.715709944</v>
+        <v>26.295594072</v>
       </c>
       <c r="P25">
-        <v>135.197683656</v>
+        <v>133.071642728</v>
       </c>
       <c r="Q25">
-        <v>152.097683656</v>
+        <v>149.971642728</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08844351098121771</v>
+        <v>0.08893051012051889</v>
       </c>
       <c r="T25">
-        <v>0.831201401349183</v>
+        <v>0.8406939210251841</v>
       </c>
       <c r="U25">
         <v>0.0613</v>
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.764838663988562</v>
+        <v>3.607970386322371</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -4154,22 +4154,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07987170769159435</v>
+        <v>0.08045374692765107</v>
       </c>
       <c r="C26">
-        <v>3140.125079030259</v>
+        <v>3032.862051278161</v>
       </c>
       <c r="D26">
-        <v>3913.289079030259</v>
+        <v>3847.562051278162</v>
       </c>
       <c r="E26">
-        <v>-1824.136</v>
+        <v>-1782.6</v>
       </c>
       <c r="F26">
-        <v>996.864</v>
+        <v>1038.4</v>
       </c>
       <c r="G26">
         <v>223.7</v>
@@ -4190,45 +4190,45 @@
         <v>220.475</v>
       </c>
       <c r="M26">
-        <v>61.1077632</v>
+        <v>66.56144</v>
       </c>
       <c r="N26">
-        <v>159.3672368</v>
+        <v>153.91356</v>
       </c>
       <c r="O26">
-        <v>26.295594072</v>
+        <v>25.3957374</v>
       </c>
       <c r="P26">
-        <v>133.071642728</v>
+        <v>128.5178226</v>
       </c>
       <c r="Q26">
-        <v>149.971642728</v>
+        <v>145.4178226</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08893051012051889</v>
+        <v>0.08943049590353476</v>
       </c>
       <c r="T26">
-        <v>0.8406939210251841</v>
+        <v>0.850439574559212</v>
       </c>
       <c r="U26">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0.165</v>
       </c>
       <c r="W26">
-        <v>0.05118549999999999</v>
+        <v>0.0535235</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.607970386322371</v>
+        <v>3.312353218319795</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -4236,22 +4236,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08045374692765107</v>
+        <v>0.08047466616370777</v>
       </c>
       <c r="C27">
-        <v>3032.862051278161</v>
+        <v>2989.004815987431</v>
       </c>
       <c r="D27">
-        <v>3847.562051278162</v>
+        <v>3845.240815987432</v>
       </c>
       <c r="E27">
-        <v>-1782.6</v>
+        <v>-1741.064</v>
       </c>
       <c r="F27">
-        <v>1038.4</v>
+        <v>1079.936</v>
       </c>
       <c r="G27">
         <v>223.7</v>
@@ -4272,28 +4272,28 @@
         <v>220.475</v>
       </c>
       <c r="M27">
-        <v>66.56144</v>
+        <v>69.22389760000002</v>
       </c>
       <c r="N27">
-        <v>153.91356</v>
+        <v>151.2511024</v>
       </c>
       <c r="O27">
-        <v>25.3957374</v>
+        <v>24.956431896</v>
       </c>
       <c r="P27">
-        <v>128.5178226</v>
+        <v>126.294670504</v>
       </c>
       <c r="Q27">
-        <v>145.4178226</v>
+        <v>143.194670504</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08943049590353476</v>
+        <v>0.08994399481582133</v>
       </c>
       <c r="T27">
-        <v>0.850439574559212</v>
+        <v>0.8604486241347001</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.312353218319795</v>
+        <v>3.184955017615188</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -4318,22 +4318,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08047466616370777</v>
+        <v>0.08049558539976449</v>
       </c>
       <c r="C28">
-        <v>2989.004815987431</v>
+        <v>2945.150379811826</v>
       </c>
       <c r="D28">
-        <v>3845.240815987432</v>
+        <v>3842.922379811827</v>
       </c>
       <c r="E28">
-        <v>-1741.064</v>
+        <v>-1699.528</v>
       </c>
       <c r="F28">
-        <v>1079.936</v>
+        <v>1121.472</v>
       </c>
       <c r="G28">
         <v>223.7</v>
@@ -4354,28 +4354,28 @@
         <v>220.475</v>
       </c>
       <c r="M28">
-        <v>69.22389760000002</v>
+        <v>71.88635520000001</v>
       </c>
       <c r="N28">
-        <v>151.2511024</v>
+        <v>148.5886448</v>
       </c>
       <c r="O28">
-        <v>24.956431896</v>
+        <v>24.517126392</v>
       </c>
       <c r="P28">
-        <v>126.294670504</v>
+        <v>124.071518408</v>
       </c>
       <c r="Q28">
-        <v>143.194670504</v>
+        <v>140.971518408</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08994399481582133</v>
+        <v>0.09047156219145822</v>
       </c>
       <c r="T28">
-        <v>0.8604486241347001</v>
+        <v>0.870731894246503</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.184955017615188</v>
+        <v>3.066993720666477</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4400,22 +4400,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08049558539976449</v>
+        <v>0.08234014463582122</v>
       </c>
       <c r="C29">
-        <v>2945.150379811826</v>
+        <v>2709.622318757368</v>
       </c>
       <c r="D29">
-        <v>3842.922379811827</v>
+        <v>3648.930318757368</v>
       </c>
       <c r="E29">
-        <v>-1699.528</v>
+        <v>-1657.992</v>
       </c>
       <c r="F29">
-        <v>1121.472</v>
+        <v>1163.008</v>
       </c>
       <c r="G29">
         <v>223.7</v>
@@ -4436,45 +4436,45 @@
         <v>220.475</v>
       </c>
       <c r="M29">
-        <v>71.88635520000001</v>
+        <v>83.62027520000002</v>
       </c>
       <c r="N29">
-        <v>148.5886448</v>
+        <v>136.8547248</v>
       </c>
       <c r="O29">
-        <v>24.517126392</v>
+        <v>22.581029592</v>
       </c>
       <c r="P29">
-        <v>124.071518408</v>
+        <v>114.273695208</v>
       </c>
       <c r="Q29">
-        <v>140.971518408</v>
+        <v>131.173695208</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09047156219145822</v>
+        <v>0.09101378421641836</v>
       </c>
       <c r="T29">
-        <v>0.870731894246503</v>
+        <v>0.8813008107503004</v>
       </c>
       <c r="U29">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V29">
         <v>0.165</v>
       </c>
       <c r="W29">
-        <v>0.0535235</v>
+        <v>0.0600365</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.066993720666477</v>
+        <v>2.636621315496459</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4482,22 +4482,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08234014463582122</v>
+        <v>0.08242619387187794</v>
       </c>
       <c r="C30">
-        <v>2709.622318757368</v>
+        <v>2659.513556120561</v>
       </c>
       <c r="D30">
-        <v>3648.930318757368</v>
+        <v>3640.357556120561</v>
       </c>
       <c r="E30">
-        <v>-1657.992</v>
+        <v>-1616.456</v>
       </c>
       <c r="F30">
-        <v>1163.008</v>
+        <v>1204.544</v>
       </c>
       <c r="G30">
         <v>223.7</v>
@@ -4518,28 +4518,28 @@
         <v>220.475</v>
       </c>
       <c r="M30">
-        <v>83.62027520000002</v>
+        <v>86.60671360000003</v>
       </c>
       <c r="N30">
-        <v>136.8547248</v>
+        <v>133.8682864</v>
       </c>
       <c r="O30">
-        <v>22.581029592</v>
+        <v>22.08826725599999</v>
       </c>
       <c r="P30">
-        <v>114.273695208</v>
+        <v>111.780019144</v>
       </c>
       <c r="Q30">
-        <v>131.173695208</v>
+        <v>128.680019144</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09101378421641836</v>
+        <v>0.09157128010123652</v>
       </c>
       <c r="T30">
-        <v>0.8813008107503004</v>
+        <v>0.8921674432119512</v>
       </c>
       <c r="U30">
         <v>0.07190000000000001</v>
@@ -4556,7 +4556,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.636621315496459</v>
+        <v>2.545703339100029</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4564,22 +4564,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08242619387187794</v>
+        <v>0.08348919310793464</v>
       </c>
       <c r="C31">
-        <v>2659.513556120561</v>
+        <v>2515.303633385009</v>
       </c>
       <c r="D31">
-        <v>3640.357556120561</v>
+        <v>3537.683633385009</v>
       </c>
       <c r="E31">
-        <v>-1616.456</v>
+        <v>-1574.92</v>
       </c>
       <c r="F31">
-        <v>1204.544</v>
+        <v>1246.08</v>
       </c>
       <c r="G31">
         <v>223.7</v>
@@ -4600,45 +4600,45 @@
         <v>220.475</v>
       </c>
       <c r="M31">
-        <v>86.60671360000002</v>
+        <v>94.45286400000002</v>
       </c>
       <c r="N31">
-        <v>133.8682864</v>
+        <v>126.022136</v>
       </c>
       <c r="O31">
-        <v>22.088267256</v>
+        <v>20.79365244</v>
       </c>
       <c r="P31">
-        <v>111.780019144</v>
+        <v>105.22848356</v>
       </c>
       <c r="Q31">
-        <v>128.680019144</v>
+        <v>122.12848356</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09157128010123652</v>
+        <v>0.09214470443990663</v>
       </c>
       <c r="T31">
-        <v>0.8921674432119512</v>
+        <v>0.903344550886792</v>
       </c>
       <c r="U31">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V31">
         <v>0.165</v>
       </c>
       <c r="W31">
-        <v>0.0600365</v>
+        <v>0.063293</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.545703339100029</v>
+        <v>2.334233083710409</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4646,22 +4646,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08348919310793464</v>
+        <v>0.08360780734399137</v>
       </c>
       <c r="C32">
-        <v>2515.303633385009</v>
+        <v>2462.668877041736</v>
       </c>
       <c r="D32">
-        <v>3537.683633385009</v>
+        <v>3526.584877041736</v>
       </c>
       <c r="E32">
-        <v>-1574.92</v>
+        <v>-1533.384</v>
       </c>
       <c r="F32">
-        <v>1246.08</v>
+        <v>1287.616</v>
       </c>
       <c r="G32">
         <v>223.7</v>
@@ -4682,28 +4682,28 @@
         <v>220.475</v>
       </c>
       <c r="M32">
-        <v>94.45286400000002</v>
+        <v>97.60129280000002</v>
       </c>
       <c r="N32">
-        <v>126.022136</v>
+        <v>122.8737072</v>
       </c>
       <c r="O32">
-        <v>20.79365244</v>
+        <v>20.274161688</v>
       </c>
       <c r="P32">
-        <v>105.22848356</v>
+        <v>102.599545512</v>
       </c>
       <c r="Q32">
-        <v>122.12848356</v>
+        <v>119.499545512</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09214470443990663</v>
+        <v>0.09273474977390053</v>
       </c>
       <c r="T32">
-        <v>0.903344550886792</v>
+        <v>0.9148456326971356</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -4720,7 +4720,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.334233083710409</v>
+        <v>2.258935242300397</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4728,22 +4728,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08360780734399137</v>
+        <v>0.08372642158004806</v>
       </c>
       <c r="C33">
-        <v>2462.668877041736</v>
+        <v>2410.103543040465</v>
       </c>
       <c r="D33">
-        <v>3526.584877041736</v>
+        <v>3515.555543040465</v>
       </c>
       <c r="E33">
-        <v>-1533.384</v>
+        <v>-1491.848</v>
       </c>
       <c r="F33">
-        <v>1287.616</v>
+        <v>1329.152</v>
       </c>
       <c r="G33">
         <v>223.7</v>
@@ -4764,28 +4764,28 @@
         <v>220.475</v>
       </c>
       <c r="M33">
-        <v>97.60129280000002</v>
+        <v>100.7497216</v>
       </c>
       <c r="N33">
-        <v>122.8737072</v>
+        <v>119.7252784</v>
       </c>
       <c r="O33">
-        <v>20.274161688</v>
+        <v>19.754670936</v>
       </c>
       <c r="P33">
-        <v>102.599545512</v>
+        <v>99.97060746399998</v>
       </c>
       <c r="Q33">
-        <v>119.499545512</v>
+        <v>116.870607464</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09273474977390053</v>
+        <v>0.09334214938242363</v>
       </c>
       <c r="T33">
-        <v>0.9148456326971356</v>
+        <v>0.9266849816195479</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.258935242300397</v>
+        <v>2.188343515978509</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4810,22 +4810,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08372642158004806</v>
+        <v>0.08384503581610478</v>
       </c>
       <c r="C34">
-        <v>2410.103543040465</v>
+        <v>2357.606982060359</v>
       </c>
       <c r="D34">
-        <v>3515.555543040465</v>
+        <v>3504.594982060359</v>
       </c>
       <c r="E34">
-        <v>-1491.848</v>
+        <v>-1450.312</v>
       </c>
       <c r="F34">
-        <v>1329.152</v>
+        <v>1370.688</v>
       </c>
       <c r="G34">
         <v>223.7</v>
@@ -4846,28 +4846,28 @@
         <v>220.475</v>
       </c>
       <c r="M34">
-        <v>100.7497216</v>
+        <v>103.8981504</v>
       </c>
       <c r="N34">
-        <v>119.7252784</v>
+        <v>116.5768496</v>
       </c>
       <c r="O34">
-        <v>19.754670936</v>
+        <v>19.235180184</v>
       </c>
       <c r="P34">
-        <v>99.97060746399998</v>
+        <v>97.34166941599997</v>
       </c>
       <c r="Q34">
-        <v>116.870607464</v>
+        <v>114.241669416</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09334214938242363</v>
+        <v>0.09396768032254446</v>
       </c>
       <c r="T34">
-        <v>0.9266849816195479</v>
+        <v>0.9388777439426294</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4884,7 +4884,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.188343515978509</v>
+        <v>2.122030076100373</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4892,22 +4892,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08384503581610478</v>
+        <v>0.0839636500521615</v>
       </c>
       <c r="C35">
-        <v>2357.606982060359</v>
+        <v>2305.17855285306</v>
       </c>
       <c r="D35">
-        <v>3504.594982060359</v>
+        <v>3493.70255285306</v>
       </c>
       <c r="E35">
-        <v>-1450.312</v>
+        <v>-1408.776</v>
       </c>
       <c r="F35">
-        <v>1370.688</v>
+        <v>1412.224</v>
       </c>
       <c r="G35">
         <v>223.7</v>
@@ -4928,28 +4928,28 @@
         <v>220.475</v>
       </c>
       <c r="M35">
-        <v>103.8981504</v>
+        <v>107.0465792</v>
       </c>
       <c r="N35">
-        <v>116.5768496</v>
+        <v>113.4284208</v>
       </c>
       <c r="O35">
-        <v>19.235180184</v>
+        <v>18.71568943199999</v>
       </c>
       <c r="P35">
-        <v>97.34166941599997</v>
+        <v>94.71273136799998</v>
       </c>
       <c r="Q35">
-        <v>114.241669416</v>
+        <v>111.612731368</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09396768032254446</v>
+        <v>0.09461216674569925</v>
       </c>
       <c r="T35">
-        <v>0.9388777439426294</v>
+        <v>0.9514399839118648</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4966,7 +4966,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.122030076100373</v>
+        <v>2.059617426803303</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0839636500521615</v>
+        <v>0.08408226428821823</v>
       </c>
       <c r="C36">
-        <v>2305.17855285306</v>
+        <v>2252.817622117611</v>
       </c>
       <c r="D36">
-        <v>3493.70255285306</v>
+        <v>3482.877622117611</v>
       </c>
       <c r="E36">
-        <v>-1408.776</v>
+        <v>-1367.24</v>
       </c>
       <c r="F36">
-        <v>1412.224</v>
+        <v>1453.76</v>
       </c>
       <c r="G36">
         <v>223.7</v>
@@ -5010,28 +5010,28 @@
         <v>220.475</v>
       </c>
       <c r="M36">
-        <v>107.0465792</v>
+        <v>110.195008</v>
       </c>
       <c r="N36">
-        <v>113.4284208</v>
+        <v>110.279992</v>
       </c>
       <c r="O36">
-        <v>18.71568943199999</v>
+        <v>18.19619867999999</v>
       </c>
       <c r="P36">
-        <v>94.71273136799998</v>
+        <v>92.08379331999997</v>
       </c>
       <c r="Q36">
-        <v>111.612731368</v>
+        <v>108.98379332</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09461216674569925</v>
+        <v>0.09527648352033574</v>
       </c>
       <c r="T36">
-        <v>0.9514399839118648</v>
+        <v>0.9643887543416921</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.059617426803303</v>
+        <v>2.000771214608922</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -5056,22 +5056,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08408226428821823</v>
+        <v>0.08846939852427493</v>
       </c>
       <c r="C37">
-        <v>2252.817622117611</v>
+        <v>1853.183027235963</v>
       </c>
       <c r="D37">
-        <v>3482.877622117611</v>
+        <v>3124.779027235963</v>
       </c>
       <c r="E37">
-        <v>-1367.24</v>
+        <v>-1325.704</v>
       </c>
       <c r="F37">
-        <v>1453.76</v>
+        <v>1495.296</v>
       </c>
       <c r="G37">
         <v>223.7</v>
@@ -5092,45 +5092,45 @@
         <v>220.475</v>
       </c>
       <c r="M37">
-        <v>110.195008</v>
+        <v>134.57664</v>
       </c>
       <c r="N37">
-        <v>110.279992</v>
+        <v>85.89835999999997</v>
       </c>
       <c r="O37">
-        <v>18.19619867999999</v>
+        <v>14.17322939999999</v>
       </c>
       <c r="P37">
-        <v>92.08379331999997</v>
+        <v>71.72513059999997</v>
       </c>
       <c r="Q37">
-        <v>108.98379332</v>
+        <v>88.62513059999998</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09527648352033574</v>
+        <v>0.09596156019417959</v>
       </c>
       <c r="T37">
-        <v>0.9643887543416921</v>
+        <v>0.9777421738474514</v>
       </c>
       <c r="U37">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V37">
         <v>0.165</v>
       </c>
       <c r="W37">
-        <v>0.063293</v>
+        <v>0.07514999999999999</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.000771214608922</v>
+        <v>1.63828581245601</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -5138,22 +5138,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08846939852427493</v>
+        <v>0.08870658276033165</v>
       </c>
       <c r="C38">
-        <v>1853.183027235963</v>
+        <v>1794.373492996218</v>
       </c>
       <c r="D38">
-        <v>3124.779027235963</v>
+        <v>3107.505492996218</v>
       </c>
       <c r="E38">
-        <v>-1325.704</v>
+        <v>-1284.168</v>
       </c>
       <c r="F38">
-        <v>1495.296</v>
+        <v>1536.832</v>
       </c>
       <c r="G38">
         <v>223.7</v>
@@ -5174,28 +5174,28 @@
         <v>220.475</v>
       </c>
       <c r="M38">
-        <v>134.57664</v>
+        <v>138.31488</v>
       </c>
       <c r="N38">
-        <v>85.89836</v>
+        <v>82.16011999999998</v>
       </c>
       <c r="O38">
-        <v>14.1732294</v>
+        <v>13.5564198</v>
       </c>
       <c r="P38">
-        <v>71.7251306</v>
+        <v>68.60370019999998</v>
       </c>
       <c r="Q38">
-        <v>88.62513060000001</v>
+        <v>85.50370019999998</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09596156019417959</v>
+        <v>0.09666838533385977</v>
       </c>
       <c r="T38">
-        <v>0.9777421738474514</v>
+        <v>0.9915195114327586</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.63828581245601</v>
+        <v>1.594007817524767</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -5220,22 +5220,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08870658276033165</v>
+        <v>0.08894376699638837</v>
       </c>
       <c r="C39">
-        <v>1794.373492996218</v>
+        <v>1735.753882368058</v>
       </c>
       <c r="D39">
-        <v>3107.505492996218</v>
+        <v>3090.421882368059</v>
       </c>
       <c r="E39">
-        <v>-1284.168</v>
+        <v>-1242.632</v>
       </c>
       <c r="F39">
-        <v>1536.832</v>
+        <v>1578.368</v>
       </c>
       <c r="G39">
         <v>223.7</v>
@@ -5256,28 +5256,28 @@
         <v>220.475</v>
       </c>
       <c r="M39">
-        <v>138.31488</v>
+        <v>142.05312</v>
       </c>
       <c r="N39">
-        <v>82.16011999999998</v>
+        <v>78.42187999999999</v>
       </c>
       <c r="O39">
-        <v>13.5564198</v>
+        <v>12.9396102</v>
       </c>
       <c r="P39">
-        <v>68.60370019999998</v>
+        <v>65.48226979999998</v>
       </c>
       <c r="Q39">
-        <v>85.50370019999998</v>
+        <v>82.38226979999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09666838533385977</v>
+        <v>0.09739801128449736</v>
       </c>
       <c r="T39">
-        <v>0.9915195114327586</v>
+        <v>1.005741279262753</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.594007817524767</v>
+        <v>1.552060243379378</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -5302,22 +5302,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08894376699638837</v>
+        <v>0.08918095123244507</v>
       </c>
       <c r="C40">
-        <v>1735.753882368058</v>
+        <v>1677.321080144086</v>
       </c>
       <c r="D40">
-        <v>3090.421882368059</v>
+        <v>3073.525080144087</v>
       </c>
       <c r="E40">
-        <v>-1242.632</v>
+        <v>-1201.096</v>
       </c>
       <c r="F40">
-        <v>1578.368</v>
+        <v>1619.904</v>
       </c>
       <c r="G40">
         <v>223.7</v>
@@ -5338,28 +5338,28 @@
         <v>220.475</v>
       </c>
       <c r="M40">
-        <v>142.05312</v>
+        <v>145.79136</v>
       </c>
       <c r="N40">
-        <v>78.42187999999999</v>
+        <v>74.68363999999997</v>
       </c>
       <c r="O40">
-        <v>12.9396102</v>
+        <v>12.3228006</v>
       </c>
       <c r="P40">
-        <v>65.48226979999998</v>
+        <v>62.36083939999997</v>
       </c>
       <c r="Q40">
-        <v>82.38226979999999</v>
+        <v>79.26083939999998</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09739801128449736</v>
+        <v>0.09815155939745095</v>
       </c>
       <c r="T40">
-        <v>1.005741279262753</v>
+        <v>1.020429334562584</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.552060243379378</v>
+        <v>1.512263826882471</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5384,22 +5384,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08918095123244507</v>
+        <v>0.1095362048728547</v>
       </c>
       <c r="C41">
-        <v>1677.321080144086</v>
+        <v>654.2019642165376</v>
       </c>
       <c r="D41">
-        <v>3073.525080144087</v>
+        <v>2091.941964216538</v>
       </c>
       <c r="E41">
-        <v>-1201.096</v>
+        <v>-1159.56</v>
       </c>
       <c r="F41">
-        <v>1619.904</v>
+        <v>1661.44</v>
       </c>
       <c r="G41">
         <v>223.7</v>
@@ -5420,45 +5420,45 @@
         <v>220.475</v>
       </c>
       <c r="M41">
-        <v>145.79136</v>
+        <v>243.8993920000001</v>
       </c>
       <c r="N41">
-        <v>74.68363999999997</v>
+        <v>-23.42439200000007</v>
       </c>
       <c r="O41">
-        <v>12.3228006</v>
+        <v>-3.865024680000011</v>
       </c>
       <c r="P41">
-        <v>62.36083939999997</v>
+        <v>-19.55936732000006</v>
       </c>
       <c r="Q41">
-        <v>79.26083939999998</v>
+        <v>-2.659367320000051</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09815155939745095</v>
+        <v>0.09929080137707424</v>
       </c>
       <c r="T41">
-        <v>1.020429334562584</v>
+        <v>1.042635281215423</v>
       </c>
       <c r="U41">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.165</v>
+        <v>0.1491532008411074</v>
       </c>
       <c r="W41">
-        <v>0.07514999999999999</v>
+        <v>0.1249043101165254</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y41">
-        <v>1.512263826882471</v>
+        <v>0.9039587929764087</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5466,22 +5466,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1095362048728547</v>
+        <v>0.1105462048728547</v>
       </c>
       <c r="C42">
-        <v>654.2019642165376</v>
+        <v>580.0329876890676</v>
       </c>
       <c r="D42">
-        <v>2091.941964216538</v>
+        <v>2059.308987689068</v>
       </c>
       <c r="E42">
-        <v>-1159.56</v>
+        <v>-1118.024</v>
       </c>
       <c r="F42">
-        <v>1661.44</v>
+        <v>1702.976</v>
       </c>
       <c r="G42">
         <v>223.7</v>
@@ -5502,37 +5502,37 @@
         <v>220.475</v>
       </c>
       <c r="M42">
-        <v>243.8993920000001</v>
+        <v>249.9968768000001</v>
       </c>
       <c r="N42">
-        <v>-23.42439200000007</v>
+        <v>-29.52187680000009</v>
       </c>
       <c r="O42">
-        <v>-3.865024680000011</v>
+        <v>-4.871109672000014</v>
       </c>
       <c r="P42">
-        <v>-19.55936732000006</v>
+        <v>-24.65076712800007</v>
       </c>
       <c r="Q42">
-        <v>-2.659367320000051</v>
+        <v>-7.750767128000067</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09929080137707424</v>
+        <v>0.1001974251292281</v>
       </c>
       <c r="T42">
-        <v>1.042635281215423</v>
+        <v>1.060307065642803</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.1491532008411074</v>
+        <v>0.1455153178937633</v>
       </c>
       <c r="W42">
-        <v>0.1249043101165254</v>
+        <v>0.1254383513331956</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.9039587929764087</v>
+        <v>0.8819110175379596</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5548,22 +5548,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1105462048728547</v>
+        <v>0.1115562048728547</v>
       </c>
       <c r="C43">
-        <v>580.0329876890676</v>
+        <v>506.8664810077946</v>
       </c>
       <c r="D43">
-        <v>2059.308987689068</v>
+        <v>2027.678481007795</v>
       </c>
       <c r="E43">
-        <v>-1118.024</v>
+        <v>-1076.488</v>
       </c>
       <c r="F43">
-        <v>1702.976</v>
+        <v>1744.512</v>
       </c>
       <c r="G43">
         <v>223.7</v>
@@ -5584,37 +5584,37 @@
         <v>220.475</v>
       </c>
       <c r="M43">
-        <v>249.9968768000001</v>
+        <v>256.0943616000001</v>
       </c>
       <c r="N43">
-        <v>-29.52187680000009</v>
+        <v>-35.61936160000008</v>
       </c>
       <c r="O43">
-        <v>-4.871109672000014</v>
+        <v>-5.877194664000013</v>
       </c>
       <c r="P43">
-        <v>-24.65076712800007</v>
+        <v>-29.74216693600006</v>
       </c>
       <c r="Q43">
-        <v>-7.750767128000067</v>
+        <v>-12.84216693600006</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1001974251292281</v>
+        <v>0.1011353117693871</v>
       </c>
       <c r="T43">
-        <v>1.060307065642803</v>
+        <v>1.07858822194699</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.1455153178937633</v>
+        <v>0.1420506674677214</v>
       </c>
       <c r="W43">
-        <v>0.1254383513331956</v>
+        <v>0.1259469620157385</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8819110175379596</v>
+        <v>0.8609131361680082</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5630,22 +5630,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1115562048728547</v>
+        <v>0.1125662048728547</v>
       </c>
       <c r="C44">
-        <v>506.8664810077948</v>
+        <v>434.6569498445688</v>
       </c>
       <c r="D44">
-        <v>2027.678481007795</v>
+        <v>1997.004949844569</v>
       </c>
       <c r="E44">
-        <v>-1076.488</v>
+        <v>-1034.952</v>
       </c>
       <c r="F44">
-        <v>1744.512</v>
+        <v>1786.048</v>
       </c>
       <c r="G44">
         <v>223.7</v>
@@ -5666,37 +5666,37 @@
         <v>220.475</v>
       </c>
       <c r="M44">
-        <v>256.0943616000001</v>
+        <v>262.1918464</v>
       </c>
       <c r="N44">
-        <v>-35.61936160000008</v>
+        <v>-41.71684640000004</v>
       </c>
       <c r="O44">
-        <v>-5.877194664000013</v>
+        <v>-6.883279656000006</v>
       </c>
       <c r="P44">
-        <v>-29.74216693600006</v>
+        <v>-34.83356674400003</v>
       </c>
       <c r="Q44">
-        <v>-12.84216693600006</v>
+        <v>-17.93356674400003</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1011353117693871</v>
+        <v>0.1021061067127097</v>
       </c>
       <c r="T44">
-        <v>1.07858822194699</v>
+        <v>1.097510822332024</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.1420506674677214</v>
+        <v>0.1387471635731232</v>
       </c>
       <c r="W44">
-        <v>0.1259469620157385</v>
+        <v>0.1264319163874655</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8609131361680082</v>
+        <v>0.840891900443171</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5712,22 +5712,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1125662048728547</v>
+        <v>0.1135762048728547</v>
       </c>
       <c r="C45">
-        <v>434.6569498445688</v>
+        <v>363.3616116944497</v>
       </c>
       <c r="D45">
-        <v>1997.004949844569</v>
+        <v>1967.24561169445</v>
       </c>
       <c r="E45">
-        <v>-1034.952</v>
+        <v>-993.4159999999999</v>
       </c>
       <c r="F45">
-        <v>1786.048</v>
+        <v>1827.584</v>
       </c>
       <c r="G45">
         <v>223.7</v>
@@ -5748,37 +5748,37 @@
         <v>220.475</v>
       </c>
       <c r="M45">
-        <v>262.1918464</v>
+        <v>268.2893312</v>
       </c>
       <c r="N45">
-        <v>-41.71684640000004</v>
+        <v>-47.81433120000005</v>
       </c>
       <c r="O45">
-        <v>-6.883279656000006</v>
+        <v>-7.88936464800001</v>
       </c>
       <c r="P45">
-        <v>-34.83356674400003</v>
+        <v>-39.92496655200004</v>
       </c>
       <c r="Q45">
-        <v>-17.93356674400003</v>
+        <v>-23.02496655200004</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1021061067127097</v>
+        <v>0.1031115729040081</v>
       </c>
       <c r="T45">
-        <v>1.097510822332024</v>
+        <v>1.117109229873668</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.1387471635731232</v>
+        <v>0.1355938189464613</v>
       </c>
       <c r="W45">
-        <v>0.1264319163874655</v>
+        <v>0.1268948273786595</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.840891900443171</v>
+        <v>0.8217807208876443</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5794,22 +5794,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1135762048728547</v>
+        <v>0.1145862048728547</v>
       </c>
       <c r="C46">
-        <v>363.3616116944497</v>
+        <v>292.9401967848173</v>
       </c>
       <c r="D46">
-        <v>1967.24561169445</v>
+        <v>1938.360196784818</v>
       </c>
       <c r="E46">
-        <v>-993.4159999999999</v>
+        <v>-951.8799999999999</v>
       </c>
       <c r="F46">
-        <v>1827.584</v>
+        <v>1869.12</v>
       </c>
       <c r="G46">
         <v>223.7</v>
@@ -5830,37 +5830,37 @@
         <v>220.475</v>
       </c>
       <c r="M46">
-        <v>268.2893312</v>
+        <v>274.3868160000001</v>
       </c>
       <c r="N46">
-        <v>-47.81433120000005</v>
+        <v>-53.91181600000007</v>
       </c>
       <c r="O46">
-        <v>-7.88936464800001</v>
+        <v>-8.895449640000013</v>
       </c>
       <c r="P46">
-        <v>-39.92496655200004</v>
+        <v>-45.01636636000006</v>
       </c>
       <c r="Q46">
-        <v>-23.02496655200004</v>
+        <v>-28.11636636000006</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1031115729040081</v>
+        <v>0.1041536015022628</v>
       </c>
       <c r="T46">
-        <v>1.117109229873668</v>
+        <v>1.137420306780462</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.1355938189464613</v>
+        <v>0.1325806229698733</v>
       </c>
       <c r="W46">
-        <v>0.1268948273786595</v>
+        <v>0.1273371645480226</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8217807208876443</v>
+        <v>0.8035189270901411</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5876,22 +5876,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1145862048728547</v>
+        <v>0.1409838114505409</v>
       </c>
       <c r="C47">
-        <v>292.9401967848173</v>
+        <v>-286.1669416346581</v>
       </c>
       <c r="D47">
-        <v>1938.360196784818</v>
+        <v>1400.789058365342</v>
       </c>
       <c r="E47">
-        <v>-951.8799999999999</v>
+        <v>-910.3439999999998</v>
       </c>
       <c r="F47">
-        <v>1869.12</v>
+        <v>1910.656</v>
       </c>
       <c r="G47">
         <v>223.7</v>
@@ -5912,45 +5912,45 @@
         <v>220.475</v>
       </c>
       <c r="M47">
-        <v>274.3868160000001</v>
+        <v>383.6597248</v>
       </c>
       <c r="N47">
-        <v>-53.91181600000007</v>
+        <v>-163.1847248000001</v>
       </c>
       <c r="O47">
-        <v>-8.895449640000013</v>
+        <v>-26.92547959200001</v>
       </c>
       <c r="P47">
-        <v>-45.01636636000006</v>
+        <v>-136.259245208</v>
       </c>
       <c r="Q47">
-        <v>-28.11636636000006</v>
+        <v>-119.359245208</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1041536015022628</v>
+        <v>0.1062483100072791</v>
       </c>
       <c r="T47">
-        <v>1.137420306780462</v>
+        <v>1.17825007442212</v>
       </c>
       <c r="U47">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1325806229698733</v>
+        <v>0.09481937417059837</v>
       </c>
       <c r="W47">
-        <v>0.1273371645480226</v>
+        <v>0.1817602696665438</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.8035189270901411</v>
+        <v>0.5746628737612022</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5958,22 +5958,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1409838114505409</v>
+        <v>0.1425338114505409</v>
       </c>
       <c r="C48">
-        <v>-286.1669416346581</v>
+        <v>-350.1482790808768</v>
       </c>
       <c r="D48">
-        <v>1400.789058365342</v>
+        <v>1378.343720919123</v>
       </c>
       <c r="E48">
-        <v>-910.3439999999998</v>
+        <v>-868.8079999999998</v>
       </c>
       <c r="F48">
-        <v>1910.656</v>
+        <v>1952.192</v>
       </c>
       <c r="G48">
         <v>223.7</v>
@@ -5994,37 +5994,37 @@
         <v>220.475</v>
       </c>
       <c r="M48">
-        <v>383.6597248</v>
+        <v>392.0001536</v>
       </c>
       <c r="N48">
-        <v>-163.1847248000001</v>
+        <v>-171.5251536</v>
       </c>
       <c r="O48">
-        <v>-26.92547959200001</v>
+        <v>-28.30165034400001</v>
       </c>
       <c r="P48">
-        <v>-136.259245208</v>
+        <v>-143.223503256</v>
       </c>
       <c r="Q48">
-        <v>-119.359245208</v>
+        <v>-126.323503256</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1062483100072791</v>
+        <v>0.1073888441583599</v>
       </c>
       <c r="T48">
-        <v>1.17825007442212</v>
+        <v>1.200481207901783</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.09481937417059837</v>
+        <v>0.09280194067760691</v>
       </c>
       <c r="W48">
-        <v>0.1817602696665438</v>
+        <v>0.1821653703119365</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5746628737612022</v>
+        <v>0.5624360041067085</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -6040,22 +6040,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1425338114505409</v>
+        <v>0.1440838114505409</v>
       </c>
       <c r="C49">
-        <v>-350.1482790808768</v>
+        <v>-413.4216612183184</v>
       </c>
       <c r="D49">
-        <v>1378.343720919123</v>
+        <v>1356.606338781682</v>
       </c>
       <c r="E49">
-        <v>-868.8079999999998</v>
+        <v>-827.2719999999997</v>
       </c>
       <c r="F49">
-        <v>1952.192</v>
+        <v>1993.728</v>
       </c>
       <c r="G49">
         <v>223.7</v>
@@ -6076,37 +6076,37 @@
         <v>220.475</v>
       </c>
       <c r="M49">
-        <v>392.0001536</v>
+        <v>400.3405824000001</v>
       </c>
       <c r="N49">
-        <v>-171.5251536</v>
+        <v>-179.8655824000001</v>
       </c>
       <c r="O49">
-        <v>-28.30165034400001</v>
+        <v>-29.67782109600001</v>
       </c>
       <c r="P49">
-        <v>-143.223503256</v>
+        <v>-150.1877613040001</v>
       </c>
       <c r="Q49">
-        <v>-126.323503256</v>
+        <v>-133.2877613040001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1073888441583599</v>
+        <v>0.1085732450075591</v>
       </c>
       <c r="T49">
-        <v>1.200481207901783</v>
+        <v>1.223567384976817</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.09280194067760691</v>
+        <v>0.0908685669134901</v>
       </c>
       <c r="W49">
-        <v>0.1821653703119365</v>
+        <v>0.1825535917637712</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5624360041067085</v>
+        <v>0.5507185873544853</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -6122,22 +6122,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1440838114505409</v>
+        <v>0.1456338114505409</v>
       </c>
       <c r="C50">
-        <v>-413.4216612183181</v>
+        <v>-476.0200627690529</v>
       </c>
       <c r="D50">
-        <v>1356.606338781682</v>
+        <v>1335.543937230947</v>
       </c>
       <c r="E50">
-        <v>-827.2719999999999</v>
+        <v>-785.7359999999999</v>
       </c>
       <c r="F50">
-        <v>1993.728</v>
+        <v>2035.264</v>
       </c>
       <c r="G50">
         <v>223.7</v>
@@ -6158,37 +6158,37 @@
         <v>220.475</v>
       </c>
       <c r="M50">
-        <v>400.3405824</v>
+        <v>408.6810112000001</v>
       </c>
       <c r="N50">
-        <v>-179.8655824</v>
+        <v>-188.2060112000001</v>
       </c>
       <c r="O50">
-        <v>-29.67782109600001</v>
+        <v>-31.05399184800001</v>
       </c>
       <c r="P50">
-        <v>-150.187761304</v>
+        <v>-157.1520193520001</v>
       </c>
       <c r="Q50">
-        <v>-133.287761304</v>
+        <v>-140.252019352</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1085732450075591</v>
+        <v>0.1098040929488838</v>
       </c>
       <c r="T50">
-        <v>1.223567384976817</v>
+        <v>1.247558902329303</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.0908685669134901</v>
+        <v>0.08901410636423519</v>
       </c>
       <c r="W50">
-        <v>0.1825535917637712</v>
+        <v>0.1829259674420616</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5507185873544855</v>
+        <v>0.5394794325105163</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -6204,22 +6204,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1456338114505409</v>
+        <v>0.1471838114505409</v>
       </c>
       <c r="C51">
-        <v>-476.0200627690529</v>
+        <v>-537.9744419273254</v>
       </c>
       <c r="D51">
-        <v>1335.543937230947</v>
+        <v>1315.125558072675</v>
       </c>
       <c r="E51">
-        <v>-785.7359999999999</v>
+        <v>-744.1999999999998</v>
       </c>
       <c r="F51">
-        <v>2035.264</v>
+        <v>2076.8</v>
       </c>
       <c r="G51">
         <v>223.7</v>
@@ -6240,37 +6240,37 @@
         <v>220.475</v>
       </c>
       <c r="M51">
-        <v>408.6810112000001</v>
+        <v>417.02144</v>
       </c>
       <c r="N51">
-        <v>-188.2060112000001</v>
+        <v>-196.54644</v>
       </c>
       <c r="O51">
-        <v>-31.05399184800001</v>
+        <v>-32.43016260000001</v>
       </c>
       <c r="P51">
-        <v>-157.1520193520001</v>
+        <v>-164.1162774</v>
       </c>
       <c r="Q51">
-        <v>-140.252019352</v>
+        <v>-147.2162774</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1098040929488838</v>
+        <v>0.1110841748078615</v>
       </c>
       <c r="T51">
-        <v>1.247558902329303</v>
+        <v>1.27251008037589</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.08901410636423519</v>
+        <v>0.0872338242369505</v>
       </c>
       <c r="W51">
-        <v>0.1829259674420616</v>
+        <v>0.1832834480932204</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5394794325105163</v>
+        <v>0.528689843860306</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -6286,22 +6286,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1471838114505409</v>
+        <v>0.1487338114505409</v>
       </c>
       <c r="C52">
-        <v>-537.9744419273254</v>
+        <v>-599.3138921861562</v>
       </c>
       <c r="D52">
-        <v>1315.125558072675</v>
+        <v>1295.322107813844</v>
       </c>
       <c r="E52">
-        <v>-744.1999999999998</v>
+        <v>-702.6639999999998</v>
       </c>
       <c r="F52">
-        <v>2076.8</v>
+        <v>2118.336</v>
       </c>
       <c r="G52">
         <v>223.7</v>
@@ -6322,37 +6322,37 @@
         <v>220.475</v>
       </c>
       <c r="M52">
-        <v>417.02144</v>
+        <v>425.3618688000001</v>
       </c>
       <c r="N52">
-        <v>-196.54644</v>
+        <v>-204.8868688000001</v>
       </c>
       <c r="O52">
-        <v>-32.43016260000001</v>
+        <v>-33.80633335200002</v>
       </c>
       <c r="P52">
-        <v>-164.1162774</v>
+        <v>-171.0805354480001</v>
       </c>
       <c r="Q52">
-        <v>-147.2162774</v>
+        <v>-154.1805354480001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1110841748078615</v>
+        <v>0.1124165049059811</v>
       </c>
       <c r="T52">
-        <v>1.27251008037589</v>
+        <v>1.298479673852948</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.0872338242369505</v>
+        <v>0.0855233570950495</v>
       </c>
       <c r="W52">
-        <v>0.1832834480932204</v>
+        <v>0.183626909895314</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.528689843860306</v>
+        <v>0.5183233763336332</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -6368,22 +6368,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1487338114505409</v>
+        <v>0.1502838114505409</v>
       </c>
       <c r="C53">
-        <v>-599.3138921861562</v>
+        <v>-660.065780650006</v>
       </c>
       <c r="D53">
-        <v>1295.322107813844</v>
+        <v>1276.106219349994</v>
       </c>
       <c r="E53">
-        <v>-702.6639999999998</v>
+        <v>-661.1279999999997</v>
       </c>
       <c r="F53">
-        <v>2118.336</v>
+        <v>2159.872</v>
       </c>
       <c r="G53">
         <v>223.7</v>
@@ -6404,37 +6404,37 @@
         <v>220.475</v>
       </c>
       <c r="M53">
-        <v>425.3618688000001</v>
+        <v>433.7022976000001</v>
       </c>
       <c r="N53">
-        <v>-204.8868688000001</v>
+        <v>-213.2272976000001</v>
       </c>
       <c r="O53">
-        <v>-33.80633335200002</v>
+        <v>-35.18250410400001</v>
       </c>
       <c r="P53">
-        <v>-171.0805354480001</v>
+        <v>-178.0447934960001</v>
       </c>
       <c r="Q53">
-        <v>-154.1805354480001</v>
+        <v>-161.1447934960001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1124165049059811</v>
+        <v>0.113804348758189</v>
       </c>
       <c r="T53">
-        <v>1.298479673852948</v>
+        <v>1.325531333724885</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.0855233570950495</v>
+        <v>0.08387867715091395</v>
       </c>
       <c r="W53">
-        <v>0.183626909895314</v>
+        <v>0.1839571616280965</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5183233763336332</v>
+        <v>0.508355619096448</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6450,22 +6450,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1502838114505409</v>
+        <v>0.1706047773189912</v>
       </c>
       <c r="C54">
-        <v>-660.065780650006</v>
+        <v>-909.3799721983069</v>
       </c>
       <c r="D54">
-        <v>1276.106219349994</v>
+        <v>1068.328027801693</v>
       </c>
       <c r="E54">
-        <v>-661.1279999999997</v>
+        <v>-619.5919999999996</v>
       </c>
       <c r="F54">
-        <v>2159.872</v>
+        <v>2201.408</v>
       </c>
       <c r="G54">
         <v>223.7</v>
@@ -6486,45 +6486,45 @@
         <v>220.475</v>
       </c>
       <c r="M54">
-        <v>433.7022976000001</v>
+        <v>519.0920064000001</v>
       </c>
       <c r="N54">
-        <v>-213.2272976000001</v>
+        <v>-298.6170064</v>
       </c>
       <c r="O54">
-        <v>-35.18250410400001</v>
+        <v>-49.27180605600001</v>
       </c>
       <c r="P54">
-        <v>-178.0447934960001</v>
+        <v>-249.345200344</v>
       </c>
       <c r="Q54">
-        <v>-161.1447934960001</v>
+        <v>-232.445200344</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.113804348758189</v>
+        <v>0.1157213899412363</v>
       </c>
       <c r="T54">
-        <v>1.325531333724885</v>
+        <v>1.362898034569354</v>
       </c>
       <c r="U54">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.08387867715091395</v>
+        <v>0.07008078443028014</v>
       </c>
       <c r="W54">
-        <v>0.1839571616280965</v>
+        <v>0.21927495103134</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.508355619096448</v>
+        <v>0.4247320268501826</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6532,22 +6532,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1706047773189912</v>
+        <v>0.1725047773189912</v>
       </c>
       <c r="C55">
-        <v>-909.3799721983069</v>
+        <v>-966.9360725905199</v>
       </c>
       <c r="D55">
-        <v>1068.328027801693</v>
+        <v>1052.30792740948</v>
       </c>
       <c r="E55">
-        <v>-619.5919999999996</v>
+        <v>-578.0559999999996</v>
       </c>
       <c r="F55">
-        <v>2201.408</v>
+        <v>2242.944</v>
       </c>
       <c r="G55">
         <v>223.7</v>
@@ -6568,37 +6568,37 @@
         <v>220.475</v>
       </c>
       <c r="M55">
-        <v>519.0920064000001</v>
+        <v>528.8861952000001</v>
       </c>
       <c r="N55">
-        <v>-298.6170064</v>
+        <v>-308.4111952000001</v>
       </c>
       <c r="O55">
-        <v>-49.27180605600001</v>
+        <v>-50.88784720800001</v>
       </c>
       <c r="P55">
-        <v>-249.345200344</v>
+        <v>-257.523347992</v>
       </c>
       <c r="Q55">
-        <v>-232.445200344</v>
+        <v>-240.623347992</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1157213899412363</v>
+        <v>0.1172414201573501</v>
       </c>
       <c r="T55">
-        <v>1.362898034569354</v>
+        <v>1.392526252712166</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.07008078443028014</v>
+        <v>0.06878299212601569</v>
       </c>
       <c r="W55">
-        <v>0.21927495103134</v>
+        <v>0.2195809704566855</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4247320268501826</v>
+        <v>0.4168666189455497</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6614,22 +6614,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1725047773189912</v>
+        <v>0.1744047773189912</v>
       </c>
       <c r="C56">
-        <v>-966.9360725905199</v>
+        <v>-1024.018812795347</v>
       </c>
       <c r="D56">
-        <v>1052.30792740948</v>
+        <v>1036.761187204653</v>
       </c>
       <c r="E56">
-        <v>-578.0559999999996</v>
+        <v>-536.5199999999995</v>
       </c>
       <c r="F56">
-        <v>2242.944</v>
+        <v>2284.48</v>
       </c>
       <c r="G56">
         <v>223.7</v>
@@ -6650,37 +6650,37 @@
         <v>220.475</v>
       </c>
       <c r="M56">
-        <v>528.8861952000001</v>
+        <v>538.6803840000001</v>
       </c>
       <c r="N56">
-        <v>-308.4111952000001</v>
+        <v>-318.2053840000001</v>
       </c>
       <c r="O56">
-        <v>-50.88784720800001</v>
+        <v>-52.50388836000002</v>
       </c>
       <c r="P56">
-        <v>-257.523347992</v>
+        <v>-265.7014956400001</v>
       </c>
       <c r="Q56">
-        <v>-240.623347992</v>
+        <v>-248.8014956400001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1172414201573501</v>
+        <v>0.1188290072719579</v>
       </c>
       <c r="T56">
-        <v>1.392526252712166</v>
+        <v>1.423471280550214</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.06878299212601569</v>
+        <v>0.06753239226917902</v>
       </c>
       <c r="W56">
-        <v>0.2195809704566855</v>
+        <v>0.2198758619029276</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4168666189455497</v>
+        <v>0.4092872258738124</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6696,22 +6696,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1744047773189912</v>
+        <v>0.1763047773189912</v>
       </c>
       <c r="C57">
-        <v>-1024.018812795347</v>
+        <v>-1080.648867558369</v>
       </c>
       <c r="D57">
-        <v>1036.761187204653</v>
+        <v>1021.667132441631</v>
       </c>
       <c r="E57">
-        <v>-536.5199999999995</v>
+        <v>-494.9839999999995</v>
       </c>
       <c r="F57">
-        <v>2284.48</v>
+        <v>2326.016000000001</v>
       </c>
       <c r="G57">
         <v>223.7</v>
@@ -6732,37 +6732,37 @@
         <v>220.475</v>
       </c>
       <c r="M57">
-        <v>538.6803840000001</v>
+        <v>548.4745728000001</v>
       </c>
       <c r="N57">
-        <v>-318.2053840000001</v>
+        <v>-327.9995728000001</v>
       </c>
       <c r="O57">
-        <v>-52.50388836000002</v>
+        <v>-54.11992951200002</v>
       </c>
       <c r="P57">
-        <v>-265.7014956400001</v>
+        <v>-273.8796432880001</v>
       </c>
       <c r="Q57">
-        <v>-248.8014956400001</v>
+        <v>-256.9796432880001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1188290072719579</v>
+        <v>0.1204887574372297</v>
       </c>
       <c r="T57">
-        <v>1.423471280550214</v>
+        <v>1.455822900562719</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06753239226917902</v>
+        <v>0.06632645669294369</v>
       </c>
       <c r="W57">
-        <v>0.2198758619029276</v>
+        <v>0.2201602215118039</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4092872258738124</v>
+        <v>0.4019785254117799</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6778,22 +6778,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1763047773189912</v>
+        <v>0.1782047773189913</v>
       </c>
       <c r="C58">
-        <v>-1080.648867558369</v>
+        <v>-1136.845724900113</v>
       </c>
       <c r="D58">
-        <v>1021.667132441631</v>
+        <v>1007.006275099887</v>
       </c>
       <c r="E58">
-        <v>-494.9839999999995</v>
+        <v>-453.4479999999994</v>
       </c>
       <c r="F58">
-        <v>2326.016000000001</v>
+        <v>2367.552000000001</v>
       </c>
       <c r="G58">
         <v>223.7</v>
@@ -6814,37 +6814,37 @@
         <v>220.475</v>
       </c>
       <c r="M58">
-        <v>548.4745728000001</v>
+        <v>558.2687616000002</v>
       </c>
       <c r="N58">
-        <v>-327.9995728000001</v>
+        <v>-337.7937616000002</v>
       </c>
       <c r="O58">
-        <v>-54.11992951200002</v>
+        <v>-55.73597066400003</v>
       </c>
       <c r="P58">
-        <v>-273.8796432880001</v>
+        <v>-282.0577909360001</v>
       </c>
       <c r="Q58">
-        <v>-256.9796432880001</v>
+        <v>-265.1577909360001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1204887574372297</v>
+        <v>0.1222257052846071</v>
       </c>
       <c r="T58">
-        <v>1.455822900562719</v>
+        <v>1.489679247087433</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06632645669294369</v>
+        <v>0.06516283464569907</v>
       </c>
       <c r="W58">
-        <v>0.2201602215118039</v>
+        <v>0.2204346035905442</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4019785254117799</v>
+        <v>0.3949262705799943</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6860,22 +6860,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1782047773189913</v>
+        <v>0.1801047773189913</v>
       </c>
       <c r="C59">
-        <v>-1136.845724900113</v>
+        <v>-1192.627770058622</v>
       </c>
       <c r="D59">
-        <v>1007.006275099887</v>
+        <v>992.7602299413786</v>
       </c>
       <c r="E59">
-        <v>-453.4479999999994</v>
+        <v>-411.9119999999994</v>
       </c>
       <c r="F59">
-        <v>2367.552000000001</v>
+        <v>2409.088000000001</v>
       </c>
       <c r="G59">
         <v>223.7</v>
@@ -6896,37 +6896,37 @@
         <v>220.475</v>
       </c>
       <c r="M59">
-        <v>558.2687616000002</v>
+        <v>568.0629504000002</v>
       </c>
       <c r="N59">
-        <v>-337.7937616000002</v>
+        <v>-347.5879504000002</v>
       </c>
       <c r="O59">
-        <v>-55.73597066400003</v>
+        <v>-57.35201181600003</v>
       </c>
       <c r="P59">
-        <v>-282.0577909360001</v>
+        <v>-290.2359385840002</v>
       </c>
       <c r="Q59">
-        <v>-265.1577909360001</v>
+        <v>-273.3359385840001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1222257052846071</v>
+        <v>0.1240453649342406</v>
       </c>
       <c r="T59">
-        <v>1.489679247087433</v>
+        <v>1.525147800589515</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06516283464569907</v>
+        <v>0.06403933749663528</v>
       </c>
       <c r="W59">
-        <v>0.2204346035905442</v>
+        <v>0.2206995242182934</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3949262705799943</v>
+        <v>0.3881171969493048</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6942,22 +6942,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1801047773189912</v>
+        <v>0.1820047773189912</v>
       </c>
       <c r="C60">
-        <v>-1192.627770058621</v>
+        <v>-1248.012362406238</v>
       </c>
       <c r="D60">
-        <v>992.760229941379</v>
+        <v>978.9116375937621</v>
       </c>
       <c r="E60">
-        <v>-411.9119999999998</v>
+        <v>-370.3759999999997</v>
       </c>
       <c r="F60">
-        <v>2409.088</v>
+        <v>2450.624</v>
       </c>
       <c r="G60">
         <v>223.7</v>
@@ -6978,37 +6978,37 @@
         <v>220.475</v>
       </c>
       <c r="M60">
-        <v>568.0629504000001</v>
+        <v>577.8571392000001</v>
       </c>
       <c r="N60">
-        <v>-347.5879504000001</v>
+        <v>-357.3821392000001</v>
       </c>
       <c r="O60">
-        <v>-57.35201181600002</v>
+        <v>-58.96805296800002</v>
       </c>
       <c r="P60">
-        <v>-290.2359385840001</v>
+        <v>-298.4140862320001</v>
       </c>
       <c r="Q60">
-        <v>-273.335938584</v>
+        <v>-281.5140862320001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1240453649342406</v>
+        <v>0.1259537884692221</v>
       </c>
       <c r="T60">
-        <v>1.525147800589515</v>
+        <v>1.562346527433162</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.06403933749663529</v>
+        <v>0.06295392499669232</v>
       </c>
       <c r="W60">
-        <v>0.2206995242182934</v>
+        <v>0.22095546448578</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3881171969493048</v>
+        <v>0.3815389393738928</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -7024,22 +7024,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1820047773189912</v>
+        <v>0.1839047773189912</v>
       </c>
       <c r="C61">
-        <v>-1248.012362406238</v>
+        <v>-1303.015906017217</v>
       </c>
       <c r="D61">
-        <v>978.9116375937621</v>
+        <v>965.444093982783</v>
       </c>
       <c r="E61">
-        <v>-370.3759999999997</v>
+        <v>-328.8399999999997</v>
       </c>
       <c r="F61">
-        <v>2450.624</v>
+        <v>2492.16</v>
       </c>
       <c r="G61">
         <v>223.7</v>
@@ -7060,37 +7060,37 @@
         <v>220.475</v>
       </c>
       <c r="M61">
-        <v>577.8571392000001</v>
+        <v>587.6513280000001</v>
       </c>
       <c r="N61">
-        <v>-357.3821392000001</v>
+        <v>-367.1763280000001</v>
       </c>
       <c r="O61">
-        <v>-58.96805296800002</v>
+        <v>-60.58409412000002</v>
       </c>
       <c r="P61">
-        <v>-298.4140862320001</v>
+        <v>-306.5922338800001</v>
       </c>
       <c r="Q61">
-        <v>-281.5140862320001</v>
+        <v>-289.6922338800001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1259537884692221</v>
+        <v>0.1279576331809526</v>
       </c>
       <c r="T61">
-        <v>1.562346527433162</v>
+        <v>1.601405190618991</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.06295392499669232</v>
+        <v>0.06190469291341411</v>
       </c>
       <c r="W61">
-        <v>0.22095546448578</v>
+        <v>0.2212028734110169</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3815389393738928</v>
+        <v>0.3751799570509946</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -7106,22 +7106,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1839047773189912</v>
+        <v>0.1858047773189912</v>
       </c>
       <c r="C62">
-        <v>-1303.015906017217</v>
+        <v>-1357.653914489313</v>
       </c>
       <c r="D62">
-        <v>965.444093982783</v>
+        <v>952.3420855106871</v>
       </c>
       <c r="E62">
-        <v>-328.8399999999997</v>
+        <v>-287.3039999999996</v>
       </c>
       <c r="F62">
-        <v>2492.16</v>
+        <v>2533.696</v>
       </c>
       <c r="G62">
         <v>223.7</v>
@@ -7142,37 +7142,37 @@
         <v>220.475</v>
       </c>
       <c r="M62">
-        <v>587.6513280000001</v>
+        <v>597.4455168000001</v>
       </c>
       <c r="N62">
-        <v>-367.1763280000001</v>
+        <v>-376.9705168</v>
       </c>
       <c r="O62">
-        <v>-60.58409412000002</v>
+        <v>-62.20013527200001</v>
       </c>
       <c r="P62">
-        <v>-306.5922338800001</v>
+        <v>-314.770381528</v>
       </c>
       <c r="Q62">
-        <v>-289.6922338800001</v>
+        <v>-297.8703815280001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1279576331809526</v>
+        <v>0.1300642391599514</v>
       </c>
       <c r="T62">
-        <v>1.601405190618991</v>
+        <v>1.642466862173323</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06190469291341411</v>
+        <v>0.06088986188204668</v>
       </c>
       <c r="W62">
-        <v>0.2212028734110169</v>
+        <v>0.2214421705682134</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3751799570509946</v>
+        <v>0.3690294659517981</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -7188,22 +7188,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1858047773189912</v>
+        <v>0.1877047773189912</v>
       </c>
       <c r="C63">
-        <v>-1357.653914489313</v>
+        <v>-1411.941070557885</v>
       </c>
       <c r="D63">
-        <v>952.3420855106871</v>
+        <v>939.5909294421157</v>
       </c>
       <c r="E63">
-        <v>-287.3039999999996</v>
+        <v>-245.7679999999996</v>
       </c>
       <c r="F63">
-        <v>2533.696</v>
+        <v>2575.232</v>
       </c>
       <c r="G63">
         <v>223.7</v>
@@ -7224,37 +7224,37 @@
         <v>220.475</v>
       </c>
       <c r="M63">
-        <v>597.4455168000001</v>
+        <v>607.2397056000001</v>
       </c>
       <c r="N63">
-        <v>-376.9705168</v>
+        <v>-386.7647056000001</v>
       </c>
       <c r="O63">
-        <v>-62.20013527200001</v>
+        <v>-63.81617642400001</v>
       </c>
       <c r="P63">
-        <v>-314.770381528</v>
+        <v>-322.9485291760001</v>
       </c>
       <c r="Q63">
-        <v>-297.8703815280001</v>
+        <v>-306.0485291760001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1300642391599514</v>
+        <v>0.1322817191378449</v>
       </c>
       <c r="T63">
-        <v>1.642466862173323</v>
+        <v>1.68568967433578</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06088986188204668</v>
+        <v>0.05990776733556205</v>
       </c>
       <c r="W63">
-        <v>0.2214421705682134</v>
+        <v>0.2216737484622745</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3690294659517981</v>
+        <v>0.3630773777912851</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -7270,22 +7270,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1877047773189912</v>
+        <v>0.1896047773189912</v>
       </c>
       <c r="C64">
-        <v>-1411.941070557885</v>
+        <v>-1465.891280984149</v>
       </c>
       <c r="D64">
-        <v>939.5909294421157</v>
+        <v>927.1767190158515</v>
       </c>
       <c r="E64">
-        <v>-245.7679999999996</v>
+        <v>-204.232</v>
       </c>
       <c r="F64">
-        <v>2575.232</v>
+        <v>2616.768</v>
       </c>
       <c r="G64">
         <v>223.7</v>
@@ -7306,37 +7306,37 @@
         <v>220.475</v>
       </c>
       <c r="M64">
-        <v>607.2397056000001</v>
+        <v>617.0338944</v>
       </c>
       <c r="N64">
-        <v>-386.7647056000001</v>
+        <v>-396.5588944</v>
       </c>
       <c r="O64">
-        <v>-63.81617642400001</v>
+        <v>-65.432217576</v>
       </c>
       <c r="P64">
-        <v>-322.9485291760001</v>
+        <v>-331.126676824</v>
       </c>
       <c r="Q64">
-        <v>-306.0485291760001</v>
+        <v>-314.226676824</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1322817191378449</v>
+        <v>0.1346190628983272</v>
       </c>
       <c r="T64">
-        <v>1.68568967433578</v>
+        <v>1.731248854723233</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05990776733556205</v>
+        <v>0.05895685039372774</v>
       </c>
       <c r="W64">
-        <v>0.2216737484622745</v>
+        <v>0.221897974677159</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3630773777912851</v>
+        <v>0.3573142448104711</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -7352,22 +7352,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1896047773189912</v>
+        <v>0.1915047773189912</v>
       </c>
       <c r="C65">
-        <v>-1465.891280984149</v>
+        <v>-1519.517727148953</v>
       </c>
       <c r="D65">
-        <v>927.1767190158515</v>
+        <v>915.0862728510467</v>
       </c>
       <c r="E65">
-        <v>-204.232</v>
+        <v>-162.6959999999999</v>
       </c>
       <c r="F65">
-        <v>2616.768</v>
+        <v>2658.304</v>
       </c>
       <c r="G65">
         <v>223.7</v>
@@ -7388,37 +7388,37 @@
         <v>220.475</v>
       </c>
       <c r="M65">
-        <v>617.0338944</v>
+        <v>626.8280832</v>
       </c>
       <c r="N65">
-        <v>-396.5588944</v>
+        <v>-406.3530832</v>
       </c>
       <c r="O65">
-        <v>-65.432217576</v>
+        <v>-67.04825872800001</v>
       </c>
       <c r="P65">
-        <v>-331.126676824</v>
+        <v>-339.304824472</v>
       </c>
       <c r="Q65">
-        <v>-314.226676824</v>
+        <v>-322.404824472</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1346190628983272</v>
+        <v>0.1370862590899474</v>
       </c>
       <c r="T65">
-        <v>1.731248854723233</v>
+        <v>1.779339100687767</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05895685039372774</v>
+        <v>0.05803564960632574</v>
       </c>
       <c r="W65">
-        <v>0.221897974677159</v>
+        <v>0.2221151938228284</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3573142448104711</v>
+        <v>0.3517312097353076</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7434,22 +7434,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1915047773189912</v>
+        <v>0.1934047773189912</v>
       </c>
       <c r="C66">
-        <v>-1519.517727148953</v>
+        <v>-1572.832911739026</v>
       </c>
       <c r="D66">
-        <v>915.0862728510467</v>
+        <v>903.3070882609741</v>
       </c>
       <c r="E66">
-        <v>-162.6959999999999</v>
+        <v>-121.1599999999999</v>
       </c>
       <c r="F66">
-        <v>2658.304</v>
+        <v>2699.84</v>
       </c>
       <c r="G66">
         <v>223.7</v>
@@ -7470,37 +7470,37 @@
         <v>220.475</v>
       </c>
       <c r="M66">
-        <v>626.8280832</v>
+        <v>636.6222720000001</v>
       </c>
       <c r="N66">
-        <v>-406.3530832</v>
+        <v>-416.147272</v>
       </c>
       <c r="O66">
-        <v>-67.04825872800001</v>
+        <v>-68.66429988000002</v>
       </c>
       <c r="P66">
-        <v>-339.304824472</v>
+        <v>-347.48297212</v>
       </c>
       <c r="Q66">
-        <v>-322.404824472</v>
+        <v>-330.58297212</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1370862590899474</v>
+        <v>0.1396944379210887</v>
       </c>
       <c r="T66">
-        <v>1.779339100687767</v>
+        <v>1.830177360707418</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05803564960632574</v>
+        <v>0.05714279345853612</v>
       </c>
       <c r="W66">
-        <v>0.2221151938228284</v>
+        <v>0.2223257293024772</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3517312097353076</v>
+        <v>0.3463199603547643</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7516,22 +7516,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1934047773189912</v>
+        <v>0.1953047773189913</v>
       </c>
       <c r="C67">
-        <v>-1572.832911739026</v>
+        <v>-1625.848701873317</v>
       </c>
       <c r="D67">
-        <v>903.3070882609741</v>
+        <v>891.8272981266833</v>
       </c>
       <c r="E67">
-        <v>-121.1599999999999</v>
+        <v>-79.6239999999998</v>
       </c>
       <c r="F67">
-        <v>2699.84</v>
+        <v>2741.376</v>
       </c>
       <c r="G67">
         <v>223.7</v>
@@ -7552,37 +7552,37 @@
         <v>220.475</v>
       </c>
       <c r="M67">
-        <v>636.6222720000001</v>
+        <v>646.4164608000001</v>
       </c>
       <c r="N67">
-        <v>-416.147272</v>
+        <v>-425.9414608000001</v>
       </c>
       <c r="O67">
-        <v>-68.66429988000002</v>
+        <v>-70.28034103200001</v>
       </c>
       <c r="P67">
-        <v>-347.48297212</v>
+        <v>-355.661119768</v>
       </c>
       <c r="Q67">
-        <v>-330.58297212</v>
+        <v>-338.7611197680001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1396944379210887</v>
+        <v>0.1424560390364149</v>
       </c>
       <c r="T67">
-        <v>1.830177360707418</v>
+        <v>1.884006106610578</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05714279345853612</v>
+        <v>0.0562769935576492</v>
       </c>
       <c r="W67">
-        <v>0.2223257293024772</v>
+        <v>0.2225298849191063</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3463199603547643</v>
+        <v>0.3410726882281769</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7598,22 +7598,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1953047773189913</v>
+        <v>0.1972047773189912</v>
       </c>
       <c r="C68">
-        <v>-1625.848701873317</v>
+        <v>-1678.576368982147</v>
       </c>
       <c r="D68">
-        <v>891.8272981266833</v>
+        <v>880.6356310178534</v>
       </c>
       <c r="E68">
-        <v>-79.6239999999998</v>
+        <v>-38.08799999999974</v>
       </c>
       <c r="F68">
-        <v>2741.376</v>
+        <v>2782.912</v>
       </c>
       <c r="G68">
         <v>223.7</v>
@@ -7634,37 +7634,37 @@
         <v>220.475</v>
       </c>
       <c r="M68">
-        <v>646.4164608000001</v>
+        <v>656.2106496000001</v>
       </c>
       <c r="N68">
-        <v>-425.9414608000001</v>
+        <v>-435.7356496000001</v>
       </c>
       <c r="O68">
-        <v>-70.28034103200001</v>
+        <v>-71.89638218400002</v>
       </c>
       <c r="P68">
-        <v>-355.661119768</v>
+        <v>-363.8392674160001</v>
       </c>
       <c r="Q68">
-        <v>-338.7611197680001</v>
+        <v>-346.9392674160001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1424560390364149</v>
+        <v>0.1453850099163062</v>
       </c>
       <c r="T68">
-        <v>1.884006106610578</v>
+        <v>1.941097200750292</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0562769935576492</v>
+        <v>0.05543703842992308</v>
       </c>
       <c r="W68">
-        <v>0.2225298849191063</v>
+        <v>0.2227279463382242</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3410726882281769</v>
+        <v>0.335982051090443</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7680,22 +7680,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1972047773189912</v>
+        <v>0.1991047773189913</v>
       </c>
       <c r="C69">
-        <v>-1678.576368982147</v>
+        <v>-1731.026625720881</v>
       </c>
       <c r="D69">
-        <v>880.6356310178534</v>
+        <v>869.7213742791191</v>
       </c>
       <c r="E69">
-        <v>-38.08799999999974</v>
+        <v>3.44800000000032</v>
       </c>
       <c r="F69">
-        <v>2782.912</v>
+        <v>2824.448</v>
       </c>
       <c r="G69">
         <v>223.7</v>
@@ -7716,37 +7716,37 @@
         <v>220.475</v>
       </c>
       <c r="M69">
-        <v>656.2106496000001</v>
+        <v>666.0048384000002</v>
       </c>
       <c r="N69">
-        <v>-435.7356496000001</v>
+        <v>-445.5298384000001</v>
       </c>
       <c r="O69">
-        <v>-71.89638218400002</v>
+        <v>-73.51242333600003</v>
       </c>
       <c r="P69">
-        <v>-363.8392674160001</v>
+        <v>-372.0174150640001</v>
       </c>
       <c r="Q69">
-        <v>-346.9392674160001</v>
+        <v>-355.1174150640001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1453850099163062</v>
+        <v>0.1484970414761908</v>
       </c>
       <c r="T69">
-        <v>1.941097200750292</v>
+        <v>2.001756488273739</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05543703842992308</v>
+        <v>0.05462178786477715</v>
       </c>
       <c r="W69">
-        <v>0.2227279463382242</v>
+        <v>0.2229201824214856</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.335982051090443</v>
+        <v>0.3310411385744071</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7762,22 +7762,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1991047773189913</v>
+        <v>0.2010047773189912</v>
       </c>
       <c r="C70">
-        <v>-1731.026625720881</v>
+        <v>-1783.209660172237</v>
       </c>
       <c r="D70">
-        <v>869.7213742791191</v>
+        <v>859.0743398277633</v>
       </c>
       <c r="E70">
-        <v>3.44800000000032</v>
+        <v>44.98400000000038</v>
       </c>
       <c r="F70">
-        <v>2824.448</v>
+        <v>2865.984</v>
       </c>
       <c r="G70">
         <v>223.7</v>
@@ -7798,37 +7798,37 @@
         <v>220.475</v>
       </c>
       <c r="M70">
-        <v>666.0048384000002</v>
+        <v>675.7990272000001</v>
       </c>
       <c r="N70">
-        <v>-445.5298384000001</v>
+        <v>-455.3240272</v>
       </c>
       <c r="O70">
-        <v>-73.51242333600003</v>
+        <v>-75.12846448800001</v>
       </c>
       <c r="P70">
-        <v>-372.0174150640001</v>
+        <v>-380.195562712</v>
       </c>
       <c r="Q70">
-        <v>-355.1174150640001</v>
+        <v>-363.295562712</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1484970414761908</v>
+        <v>0.1518098492657454</v>
       </c>
       <c r="T70">
-        <v>2.001756488273739</v>
+        <v>2.066329278218053</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05462178786477715</v>
+        <v>0.05383016775079489</v>
       </c>
       <c r="W70">
-        <v>0.2229201824214856</v>
+        <v>0.2231068464443626</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3310411385744071</v>
+        <v>0.3262434409139084</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7844,22 +7844,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2010047773189912</v>
+        <v>0.2029047773189912</v>
       </c>
       <c r="C71">
-        <v>-1783.209660172237</v>
+        <v>-1835.135167566774</v>
       </c>
       <c r="D71">
-        <v>859.0743398277633</v>
+        <v>848.6848324332266</v>
       </c>
       <c r="E71">
-        <v>44.98400000000038</v>
+        <v>86.52000000000044</v>
       </c>
       <c r="F71">
-        <v>2865.984</v>
+        <v>2907.52</v>
       </c>
       <c r="G71">
         <v>223.7</v>
@@ -7880,37 +7880,37 @@
         <v>220.475</v>
       </c>
       <c r="M71">
-        <v>675.7990272000001</v>
+        <v>685.5932160000001</v>
       </c>
       <c r="N71">
-        <v>-455.3240272</v>
+        <v>-465.1182160000001</v>
       </c>
       <c r="O71">
-        <v>-75.12846448800001</v>
+        <v>-76.74450564000001</v>
       </c>
       <c r="P71">
-        <v>-380.195562712</v>
+        <v>-388.3737103600001</v>
       </c>
       <c r="Q71">
-        <v>-363.295562712</v>
+        <v>-371.47371036</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1518098492657454</v>
+        <v>0.1553435109079369</v>
       </c>
       <c r="T71">
-        <v>2.066329278218053</v>
+        <v>2.135206920825321</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05383016775079489</v>
+        <v>0.05306116535435496</v>
       </c>
       <c r="W71">
-        <v>0.2231068464443626</v>
+        <v>0.2232881772094431</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3262434409139084</v>
+        <v>0.321582820329424</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7926,22 +7926,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2029047773189912</v>
+        <v>0.2048047773189912</v>
       </c>
       <c r="C72">
-        <v>-1835.135167566774</v>
+        <v>-1886.812379729149</v>
       </c>
       <c r="D72">
-        <v>848.6848324332266</v>
+        <v>838.5436202708511</v>
       </c>
       <c r="E72">
-        <v>86.52000000000044</v>
+        <v>128.0560000000005</v>
       </c>
       <c r="F72">
-        <v>2907.52</v>
+        <v>2949.056</v>
       </c>
       <c r="G72">
         <v>223.7</v>
@@ -7962,37 +7962,37 @@
         <v>220.475</v>
       </c>
       <c r="M72">
-        <v>685.5932160000001</v>
+        <v>695.3874048000001</v>
       </c>
       <c r="N72">
-        <v>-465.1182160000001</v>
+        <v>-474.9124048000001</v>
       </c>
       <c r="O72">
-        <v>-76.74450564000001</v>
+        <v>-78.36054679200002</v>
       </c>
       <c r="P72">
-        <v>-388.3737103600001</v>
+        <v>-396.5518580080001</v>
       </c>
       <c r="Q72">
-        <v>-371.47371036</v>
+        <v>-379.6518580080001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1553435109079369</v>
+        <v>0.1591208733530382</v>
       </c>
       <c r="T72">
-        <v>2.135206920825321</v>
+        <v>2.208834745681367</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05306116535435496</v>
+        <v>0.05231382499725137</v>
       </c>
       <c r="W72">
-        <v>0.2232881772094431</v>
+        <v>0.2234644000656481</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.321582820329424</v>
+        <v>0.3170534848318265</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -8008,22 +8008,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2048047773189912</v>
+        <v>0.2067047773189912</v>
       </c>
       <c r="C73">
-        <v>-1886.812379729149</v>
+        <v>-1938.250092438126</v>
       </c>
       <c r="D73">
-        <v>838.5436202708511</v>
+        <v>828.6419075618739</v>
       </c>
       <c r="E73">
-        <v>128.056</v>
+        <v>169.5920000000001</v>
       </c>
       <c r="F73">
-        <v>2949.056</v>
+        <v>2990.592</v>
       </c>
       <c r="G73">
         <v>223.7</v>
@@ -8044,37 +8044,37 @@
         <v>220.475</v>
       </c>
       <c r="M73">
-        <v>695.3874048</v>
+        <v>705.1815936</v>
       </c>
       <c r="N73">
-        <v>-474.9124048</v>
+        <v>-484.7065936</v>
       </c>
       <c r="O73">
-        <v>-78.36054679200001</v>
+        <v>-79.976587944</v>
       </c>
       <c r="P73">
-        <v>-396.551858008</v>
+        <v>-404.730005656</v>
       </c>
       <c r="Q73">
-        <v>-379.651858008</v>
+        <v>-387.830005656</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1591208733530381</v>
+        <v>0.1631680474013609</v>
       </c>
       <c r="T73">
-        <v>2.208834745681366</v>
+        <v>2.287721700884272</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05231382499725137</v>
+        <v>0.05158724409451177</v>
       </c>
       <c r="W73">
-        <v>0.2234644000656481</v>
+        <v>0.2236357278425141</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3170534848318265</v>
+        <v>0.3126499642091622</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -8090,22 +8090,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2067047773189912</v>
+        <v>0.2086047773189912</v>
       </c>
       <c r="C74">
-        <v>-1938.250092438126</v>
+        <v>-1989.456690870768</v>
       </c>
       <c r="D74">
-        <v>828.6419075618739</v>
+        <v>818.9713091292324</v>
       </c>
       <c r="E74">
-        <v>169.5920000000001</v>
+        <v>211.1280000000002</v>
       </c>
       <c r="F74">
-        <v>2990.592</v>
+        <v>3032.128</v>
       </c>
       <c r="G74">
         <v>223.7</v>
@@ -8126,37 +8126,37 @@
         <v>220.475</v>
       </c>
       <c r="M74">
-        <v>705.1815936</v>
+        <v>714.9757824000001</v>
       </c>
       <c r="N74">
-        <v>-484.7065936</v>
+        <v>-494.5007824</v>
       </c>
       <c r="O74">
-        <v>-79.976587944</v>
+        <v>-81.59262909600001</v>
       </c>
       <c r="P74">
-        <v>-404.730005656</v>
+        <v>-412.9081533040001</v>
       </c>
       <c r="Q74">
-        <v>-387.830005656</v>
+        <v>-396.0081533040001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1631680474013609</v>
+        <v>0.1675150121199298</v>
       </c>
       <c r="T74">
-        <v>2.287721700884272</v>
+        <v>2.372452134250356</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05158724409451177</v>
+        <v>0.05088056951787462</v>
       </c>
       <c r="W74">
-        <v>0.2236357278425141</v>
+        <v>0.2238023617076852</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3126499642091622</v>
+        <v>0.308367087987119</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -8172,22 +8172,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2086047773189912</v>
+        <v>0.2105047773189913</v>
       </c>
       <c r="C75">
-        <v>-1989.456690870768</v>
+        <v>-2040.440173285512</v>
       </c>
       <c r="D75">
-        <v>818.9713091292324</v>
+        <v>809.5238267144882</v>
       </c>
       <c r="E75">
-        <v>211.1280000000002</v>
+        <v>252.6640000000002</v>
       </c>
       <c r="F75">
-        <v>3032.128</v>
+        <v>3073.664</v>
       </c>
       <c r="G75">
         <v>223.7</v>
@@ -8208,37 +8208,37 @@
         <v>220.475</v>
       </c>
       <c r="M75">
-        <v>714.9757824000001</v>
+        <v>724.7699712000001</v>
       </c>
       <c r="N75">
-        <v>-494.5007824</v>
+        <v>-504.2949712000001</v>
       </c>
       <c r="O75">
-        <v>-81.59262909600001</v>
+        <v>-83.20867024800002</v>
       </c>
       <c r="P75">
-        <v>-412.9081533040001</v>
+        <v>-421.086300952</v>
       </c>
       <c r="Q75">
-        <v>-396.0081533040001</v>
+        <v>-404.186300952</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1675150121199298</v>
+        <v>0.1721963587399271</v>
       </c>
       <c r="T75">
-        <v>2.372452134250356</v>
+        <v>2.463700293259985</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05088056951787462</v>
+        <v>0.05019299425411955</v>
       </c>
       <c r="W75">
-        <v>0.2238023617076852</v>
+        <v>0.2239644919548786</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.308367087987119</v>
+        <v>0.3041999651764822</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -8254,22 +8254,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2105047773189913</v>
+        <v>0.2124047773189912</v>
       </c>
       <c r="C76">
-        <v>-2040.440173285512</v>
+        <v>-2091.208173084729</v>
       </c>
       <c r="D76">
-        <v>809.5238267144882</v>
+        <v>800.2918269152714</v>
       </c>
       <c r="E76">
-        <v>252.6640000000002</v>
+        <v>294.2000000000003</v>
       </c>
       <c r="F76">
-        <v>3073.664</v>
+        <v>3115.2</v>
       </c>
       <c r="G76">
         <v>223.7</v>
@@ -8290,37 +8290,37 @@
         <v>220.475</v>
       </c>
       <c r="M76">
-        <v>724.7699712000001</v>
+        <v>734.5641600000001</v>
       </c>
       <c r="N76">
-        <v>-504.2949712000001</v>
+        <v>-514.0891600000001</v>
       </c>
       <c r="O76">
-        <v>-83.20867024800002</v>
+        <v>-84.82471140000003</v>
       </c>
       <c r="P76">
-        <v>-421.086300952</v>
+        <v>-429.2644486000001</v>
       </c>
       <c r="Q76">
-        <v>-404.186300952</v>
+        <v>-412.3644486000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1721963587399271</v>
+        <v>0.1772522130895242</v>
       </c>
       <c r="T76">
-        <v>2.463700293259985</v>
+        <v>2.562248304990385</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05019299425411955</v>
+        <v>0.04952375433073129</v>
       </c>
       <c r="W76">
-        <v>0.2239644919548786</v>
+        <v>0.2241222987288136</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3041999651764822</v>
+        <v>0.3001439656407957</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -8336,22 +8336,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2124047773189912</v>
+        <v>0.2143047773189913</v>
       </c>
       <c r="C77">
-        <v>-2091.208173084729</v>
+        <v>-2141.767979384657</v>
       </c>
       <c r="D77">
-        <v>800.2918269152714</v>
+        <v>791.2680206153434</v>
       </c>
       <c r="E77">
-        <v>294.2000000000003</v>
+        <v>335.7360000000003</v>
       </c>
       <c r="F77">
-        <v>3115.2</v>
+        <v>3156.736</v>
       </c>
       <c r="G77">
         <v>223.7</v>
@@ -8372,37 +8372,37 @@
         <v>220.475</v>
       </c>
       <c r="M77">
-        <v>734.5641600000001</v>
+        <v>744.3583488000002</v>
       </c>
       <c r="N77">
-        <v>-514.0891600000001</v>
+        <v>-523.8833488000001</v>
       </c>
       <c r="O77">
-        <v>-84.82471140000003</v>
+        <v>-86.44075255200002</v>
       </c>
       <c r="P77">
-        <v>-429.2644486000001</v>
+        <v>-437.4425962480001</v>
       </c>
       <c r="Q77">
-        <v>-412.3644486000001</v>
+        <v>-420.5425962480001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1772522130895242</v>
+        <v>0.1827293886349211</v>
       </c>
       <c r="T77">
-        <v>2.562248304990385</v>
+        <v>2.669008651031652</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04952375433073129</v>
+        <v>0.0488721259842743</v>
       </c>
       <c r="W77">
-        <v>0.2241222987288136</v>
+        <v>0.2242759526929081</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3001439656407957</v>
+        <v>0.2961947029349958</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8418,22 +8418,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2143047773189913</v>
+        <v>0.2162047773189912</v>
       </c>
       <c r="C78">
-        <v>-2141.767979384657</v>
+        <v>-2192.126556209219</v>
       </c>
       <c r="D78">
-        <v>791.2680206153434</v>
+        <v>782.4454437907818</v>
       </c>
       <c r="E78">
-        <v>335.7360000000003</v>
+        <v>377.2720000000004</v>
       </c>
       <c r="F78">
-        <v>3156.736</v>
+        <v>3198.272</v>
       </c>
       <c r="G78">
         <v>223.7</v>
@@ -8454,37 +8454,37 @@
         <v>220.475</v>
       </c>
       <c r="M78">
-        <v>744.3583488000002</v>
+        <v>754.1525376000001</v>
       </c>
       <c r="N78">
-        <v>-523.8833488000001</v>
+        <v>-533.6775376000001</v>
       </c>
       <c r="O78">
-        <v>-86.44075255200002</v>
+        <v>-88.05679370400001</v>
       </c>
       <c r="P78">
-        <v>-437.4425962480001</v>
+        <v>-445.620743896</v>
       </c>
       <c r="Q78">
-        <v>-420.5425962480001</v>
+        <v>-428.720743896</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1827293886349211</v>
+        <v>0.1886828403147003</v>
       </c>
       <c r="T78">
-        <v>2.669008651031652</v>
+        <v>2.785052505424332</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0488721259842743</v>
+        <v>0.0482374230494136</v>
       </c>
       <c r="W78">
-        <v>0.2242759526929081</v>
+        <v>0.2244256156449483</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2961947029349958</v>
+        <v>0.2923480184812945</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8500,22 +8500,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2162047773189912</v>
+        <v>0.2181047773189912</v>
       </c>
       <c r="C79">
-        <v>-2192.126556209219</v>
+        <v>-2242.290560413944</v>
       </c>
       <c r="D79">
-        <v>782.4454437907818</v>
+        <v>773.8174395860564</v>
       </c>
       <c r="E79">
-        <v>377.2720000000004</v>
+        <v>418.8080000000004</v>
       </c>
       <c r="F79">
-        <v>3198.272</v>
+        <v>3239.808</v>
       </c>
       <c r="G79">
         <v>223.7</v>
@@ -8536,37 +8536,37 @@
         <v>220.475</v>
       </c>
       <c r="M79">
-        <v>754.1525376000001</v>
+        <v>763.9467264000001</v>
       </c>
       <c r="N79">
-        <v>-533.6775376000001</v>
+        <v>-543.4717264000001</v>
       </c>
       <c r="O79">
-        <v>-88.05679370400001</v>
+        <v>-89.67283485600002</v>
       </c>
       <c r="P79">
-        <v>-445.620743896</v>
+        <v>-453.7988915440001</v>
       </c>
       <c r="Q79">
-        <v>-428.720743896</v>
+        <v>-436.8988915440001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1886828403147003</v>
+        <v>0.1951775148744594</v>
       </c>
       <c r="T79">
-        <v>2.785052505424332</v>
+        <v>2.911645801125438</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0482374230494136</v>
+        <v>0.04761899454878009</v>
       </c>
       <c r="W79">
-        <v>0.2244256156449483</v>
+        <v>0.2245714410853977</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2923480184812945</v>
+        <v>0.2885999669623036</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8582,22 +8582,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2181047773189912</v>
+        <v>0.2200047773189912</v>
       </c>
       <c r="C80">
-        <v>-2242.290560413944</v>
+        <v>-2292.266358436941</v>
       </c>
       <c r="D80">
-        <v>773.8174395860564</v>
+        <v>765.3776415630593</v>
       </c>
       <c r="E80">
-        <v>418.8080000000004</v>
+        <v>460.3440000000005</v>
       </c>
       <c r="F80">
-        <v>3239.808</v>
+        <v>3281.344000000001</v>
       </c>
       <c r="G80">
         <v>223.7</v>
@@ -8618,37 +8618,37 @@
         <v>220.475</v>
       </c>
       <c r="M80">
-        <v>763.9467264000001</v>
+        <v>773.7409152000001</v>
       </c>
       <c r="N80">
-        <v>-543.4717264000001</v>
+        <v>-553.2659152000001</v>
       </c>
       <c r="O80">
-        <v>-89.67283485600002</v>
+        <v>-91.28887600800002</v>
       </c>
       <c r="P80">
-        <v>-453.7988915440001</v>
+        <v>-461.9770391920001</v>
       </c>
       <c r="Q80">
-        <v>-436.8988915440001</v>
+        <v>-445.0770391920001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1951775148744594</v>
+        <v>0.2022907298684813</v>
       </c>
       <c r="T80">
-        <v>2.911645801125438</v>
+        <v>3.05029560117903</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04761899454878009</v>
+        <v>0.04701622246588414</v>
       </c>
       <c r="W80">
-        <v>0.2245714410853977</v>
+        <v>0.2247135747425445</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2885999669623036</v>
+        <v>0.2849468028235402</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8664,22 +8664,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2200047773189912</v>
+        <v>0.2219047773189912</v>
       </c>
       <c r="C81">
-        <v>-2292.266358436941</v>
+        <v>-2342.060041965513</v>
       </c>
       <c r="D81">
-        <v>765.3776415630593</v>
+        <v>757.1199580344876</v>
       </c>
       <c r="E81">
-        <v>460.3440000000005</v>
+        <v>501.8800000000006</v>
       </c>
       <c r="F81">
-        <v>3281.344000000001</v>
+        <v>3322.880000000001</v>
       </c>
       <c r="G81">
         <v>223.7</v>
@@ -8700,37 +8700,37 @@
         <v>220.475</v>
       </c>
       <c r="M81">
-        <v>773.7409152000001</v>
+        <v>783.5351040000002</v>
       </c>
       <c r="N81">
-        <v>-553.2659152000001</v>
+        <v>-563.0601040000001</v>
       </c>
       <c r="O81">
-        <v>-91.28887600800002</v>
+        <v>-92.90491716000002</v>
       </c>
       <c r="P81">
-        <v>-461.9770391920001</v>
+        <v>-470.1551868400001</v>
       </c>
       <c r="Q81">
-        <v>-445.0770391920001</v>
+        <v>-453.2551868400001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2022907298684813</v>
+        <v>0.2101152663619053</v>
       </c>
       <c r="T81">
-        <v>3.05029560117903</v>
+        <v>3.202810381237982</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04701622246588414</v>
+        <v>0.04642851968506059</v>
       </c>
       <c r="W81">
-        <v>0.2247135747425445</v>
+        <v>0.2248521550582627</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2849468028235402</v>
+        <v>0.281384967788246</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8746,22 +8746,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2219047773189912</v>
+        <v>0.2238047773189912</v>
       </c>
       <c r="C82">
-        <v>-2342.060041965513</v>
+        <v>-2391.677442599428</v>
       </c>
       <c r="D82">
-        <v>757.1199580344876</v>
+        <v>749.038557400573</v>
       </c>
       <c r="E82">
-        <v>501.8800000000006</v>
+        <v>543.4160000000006</v>
       </c>
       <c r="F82">
-        <v>3322.880000000001</v>
+        <v>3364.416000000001</v>
       </c>
       <c r="G82">
         <v>223.7</v>
@@ -8782,37 +8782,37 @@
         <v>220.475</v>
       </c>
       <c r="M82">
-        <v>783.5351040000002</v>
+        <v>793.3292928000002</v>
       </c>
       <c r="N82">
-        <v>-563.0601040000001</v>
+        <v>-572.8542928000002</v>
       </c>
       <c r="O82">
-        <v>-92.90491716000002</v>
+        <v>-94.52095831200003</v>
       </c>
       <c r="P82">
-        <v>-470.1551868400001</v>
+        <v>-478.3333344880001</v>
       </c>
       <c r="Q82">
-        <v>-453.2551868400001</v>
+        <v>-461.4333344880001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2101152663619053</v>
+        <v>0.2187634382756898</v>
       </c>
       <c r="T82">
-        <v>3.202810381237982</v>
+        <v>3.37137934867156</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04642851968506059</v>
+        <v>0.04585532808401045</v>
       </c>
       <c r="W82">
-        <v>0.2248521550582627</v>
+        <v>0.2249873136377903</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.281384967788246</v>
+        <v>0.2779110792970331</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8828,22 +8828,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2238047773189912</v>
+        <v>0.2257047773189912</v>
       </c>
       <c r="C83">
-        <v>-2391.677442599428</v>
+        <v>-2441.124145585028</v>
       </c>
       <c r="D83">
-        <v>749.038557400573</v>
+        <v>741.1278544149727</v>
       </c>
       <c r="E83">
-        <v>543.4160000000006</v>
+        <v>584.9520000000007</v>
       </c>
       <c r="F83">
-        <v>3364.416000000001</v>
+        <v>3405.952000000001</v>
       </c>
       <c r="G83">
         <v>223.7</v>
@@ -8864,37 +8864,37 @@
         <v>220.475</v>
       </c>
       <c r="M83">
-        <v>793.3292928000002</v>
+        <v>803.1234816000002</v>
       </c>
       <c r="N83">
-        <v>-572.8542928000002</v>
+        <v>-582.6484816000002</v>
       </c>
       <c r="O83">
-        <v>-94.52095831200003</v>
+        <v>-96.13699946400004</v>
       </c>
       <c r="P83">
-        <v>-478.3333344880001</v>
+        <v>-486.5114821360002</v>
       </c>
       <c r="Q83">
-        <v>-461.4333344880001</v>
+        <v>-469.6114821360002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2187634382756898</v>
+        <v>0.2283725181798948</v>
       </c>
       <c r="T83">
-        <v>3.37137934867156</v>
+        <v>3.558678201375536</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04585532808401045</v>
+        <v>0.04529611676591276</v>
       </c>
       <c r="W83">
-        <v>0.2249873136377903</v>
+        <v>0.2251191756665978</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2779110792970331</v>
+        <v>0.2745219197934107</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8910,22 +8910,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2257047773189912</v>
+        <v>0.2276047773189912</v>
       </c>
       <c r="C84">
-        <v>-2441.124145585028</v>
+        <v>-2490.405502688146</v>
       </c>
       <c r="D84">
-        <v>741.1278544149727</v>
+        <v>733.3824973118549</v>
       </c>
       <c r="E84">
-        <v>584.9520000000007</v>
+        <v>626.4880000000007</v>
       </c>
       <c r="F84">
-        <v>3405.952000000001</v>
+        <v>3447.488000000001</v>
       </c>
       <c r="G84">
         <v>223.7</v>
@@ -8946,37 +8946,37 @@
         <v>220.475</v>
       </c>
       <c r="M84">
-        <v>803.1234816000002</v>
+        <v>812.9176704000002</v>
       </c>
       <c r="N84">
-        <v>-582.6484816000002</v>
+        <v>-592.4426704000002</v>
       </c>
       <c r="O84">
-        <v>-96.13699946400004</v>
+        <v>-97.75304061600004</v>
       </c>
       <c r="P84">
-        <v>-486.5114821360002</v>
+        <v>-494.6896297840002</v>
       </c>
       <c r="Q84">
-        <v>-469.6114821360002</v>
+        <v>-477.7896297840002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2283725181798948</v>
+        <v>0.2391120780728298</v>
       </c>
       <c r="T84">
-        <v>3.558678201375536</v>
+        <v>3.768012213221156</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04529611676591276</v>
+        <v>0.0447503804193355</v>
       </c>
       <c r="W84">
-        <v>0.2251191756665978</v>
+        <v>0.2252478602971207</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2745219197934107</v>
+        <v>0.2712144267838515</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8992,22 +8992,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2276047773189912</v>
+        <v>0.2295047773189913</v>
       </c>
       <c r="C85">
-        <v>-2490.405502688146</v>
+        <v>-2539.526644268177</v>
       </c>
       <c r="D85">
-        <v>733.3824973118549</v>
+        <v>725.797355731824</v>
       </c>
       <c r="E85">
-        <v>626.4880000000007</v>
+        <v>668.0240000000008</v>
       </c>
       <c r="F85">
-        <v>3447.488000000001</v>
+        <v>3489.024000000001</v>
       </c>
       <c r="G85">
         <v>223.7</v>
@@ -9028,37 +9028,37 @@
         <v>220.475</v>
       </c>
       <c r="M85">
-        <v>812.9176704000002</v>
+        <v>822.7118592000003</v>
       </c>
       <c r="N85">
-        <v>-592.4426704000002</v>
+        <v>-602.2368592000003</v>
       </c>
       <c r="O85">
-        <v>-97.75304061600004</v>
+        <v>-99.36908176800004</v>
       </c>
       <c r="P85">
-        <v>-494.6896297840002</v>
+        <v>-502.8677774320002</v>
       </c>
       <c r="Q85">
-        <v>-477.7896297840002</v>
+        <v>-485.9677774320002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2391120780728298</v>
+        <v>0.2511940829523817</v>
       </c>
       <c r="T85">
-        <v>3.768012213221156</v>
+        <v>4.003512976547479</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0447503804193355</v>
+        <v>0.04421763779529578</v>
       </c>
       <c r="W85">
-        <v>0.2252478602971207</v>
+        <v>0.2253734810078693</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2712144267838515</v>
+        <v>0.2679856836078532</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -9074,22 +9074,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2295047773189912</v>
+        <v>0.2314047773189912</v>
       </c>
       <c r="C86">
-        <v>-2539.526644268176</v>
+        <v>-2588.492490610549</v>
       </c>
       <c r="D86">
-        <v>725.797355731824</v>
+        <v>718.3675093894514</v>
       </c>
       <c r="E86">
-        <v>668.0240000000003</v>
+        <v>709.5600000000004</v>
       </c>
       <c r="F86">
-        <v>3489.024</v>
+        <v>3530.56</v>
       </c>
       <c r="G86">
         <v>223.7</v>
@@ -9110,37 +9110,37 @@
         <v>220.475</v>
       </c>
       <c r="M86">
-        <v>822.7118592000002</v>
+        <v>832.5060480000001</v>
       </c>
       <c r="N86">
-        <v>-602.2368592000001</v>
+        <v>-612.0310480000001</v>
       </c>
       <c r="O86">
-        <v>-99.36908176800003</v>
+        <v>-100.98512292</v>
       </c>
       <c r="P86">
-        <v>-502.8677774320001</v>
+        <v>-511.0459250800001</v>
       </c>
       <c r="Q86">
-        <v>-485.9677774320002</v>
+        <v>-494.1459250800001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2511940829523816</v>
+        <v>0.2648870218158737</v>
       </c>
       <c r="T86">
-        <v>4.003512976547476</v>
+        <v>4.270413841650641</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0442176377952958</v>
+        <v>0.04369743029182174</v>
       </c>
       <c r="W86">
-        <v>0.2253734810078693</v>
+        <v>0.2254961459371884</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2679856836078534</v>
+        <v>0.2648329108595256</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -9156,22 +9156,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2314047773189912</v>
+        <v>0.2333047773189912</v>
       </c>
       <c r="C87">
-        <v>-2588.492490610549</v>
+        <v>-2637.307762570207</v>
       </c>
       <c r="D87">
-        <v>718.3675093894514</v>
+        <v>711.0882374297935</v>
       </c>
       <c r="E87">
-        <v>709.5600000000004</v>
+        <v>751.0960000000005</v>
       </c>
       <c r="F87">
-        <v>3530.56</v>
+        <v>3572.096</v>
       </c>
       <c r="G87">
         <v>223.7</v>
@@ -9192,37 +9192,37 @@
         <v>220.475</v>
       </c>
       <c r="M87">
-        <v>832.5060480000001</v>
+        <v>842.3002368000001</v>
       </c>
       <c r="N87">
-        <v>-612.0310480000001</v>
+        <v>-621.8252368000001</v>
       </c>
       <c r="O87">
-        <v>-100.98512292</v>
+        <v>-102.601164072</v>
       </c>
       <c r="P87">
-        <v>-511.0459250800001</v>
+        <v>-519.224072728</v>
       </c>
       <c r="Q87">
-        <v>-494.1459250800001</v>
+        <v>-502.324072728</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2648870218158737</v>
+        <v>0.2805360948027218</v>
       </c>
       <c r="T87">
-        <v>4.270413841650641</v>
+        <v>4.575443401768544</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04369743029182174</v>
+        <v>0.04318932063726566</v>
       </c>
       <c r="W87">
-        <v>0.2254961459371884</v>
+        <v>0.2256159581937328</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2648329108595256</v>
+        <v>0.2617534584076707</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -9238,22 +9238,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2333047773189912</v>
+        <v>0.2352047773189912</v>
       </c>
       <c r="C88">
-        <v>-2637.307762570207</v>
+        <v>-2685.976991574464</v>
       </c>
       <c r="D88">
-        <v>711.0882374297935</v>
+        <v>703.9550084255371</v>
       </c>
       <c r="E88">
-        <v>751.0960000000005</v>
+        <v>792.6320000000005</v>
       </c>
       <c r="F88">
-        <v>3572.096</v>
+        <v>3613.632000000001</v>
       </c>
       <c r="G88">
         <v>223.7</v>
@@ -9274,37 +9274,37 @@
         <v>220.475</v>
       </c>
       <c r="M88">
-        <v>842.3002368000001</v>
+        <v>852.0944256000001</v>
       </c>
       <c r="N88">
-        <v>-621.8252368000001</v>
+        <v>-631.6194256000001</v>
       </c>
       <c r="O88">
-        <v>-102.601164072</v>
+        <v>-104.217205224</v>
       </c>
       <c r="P88">
-        <v>-519.224072728</v>
+        <v>-527.4022203760001</v>
       </c>
       <c r="Q88">
-        <v>-502.324072728</v>
+        <v>-510.5022203760001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2805360948027218</v>
+        <v>0.2985927174798543</v>
       </c>
       <c r="T88">
-        <v>4.575443401768544</v>
+        <v>4.927400586519971</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04318932063726566</v>
+        <v>0.04269289166442353</v>
       </c>
       <c r="W88">
-        <v>0.2256159581937328</v>
+        <v>0.2257330161455289</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2617534584076707</v>
+        <v>0.2587447979662032</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -9320,22 +9320,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2352047773189912</v>
+        <v>0.2371047773189913</v>
       </c>
       <c r="C89">
-        <v>-2685.976991574464</v>
+        <v>-2734.504529029789</v>
       </c>
       <c r="D89">
-        <v>703.9550084255371</v>
+        <v>696.963470970211</v>
       </c>
       <c r="E89">
-        <v>792.6320000000005</v>
+        <v>834.1680000000001</v>
       </c>
       <c r="F89">
-        <v>3613.632000000001</v>
+        <v>3655.168</v>
       </c>
       <c r="G89">
         <v>223.7</v>
@@ -9356,37 +9356,37 @@
         <v>220.475</v>
       </c>
       <c r="M89">
-        <v>852.0944256000001</v>
+        <v>861.8886144000001</v>
       </c>
       <c r="N89">
-        <v>-631.6194256000001</v>
+        <v>-641.4136144</v>
       </c>
       <c r="O89">
-        <v>-104.217205224</v>
+        <v>-105.833246376</v>
       </c>
       <c r="P89">
-        <v>-527.4022203760001</v>
+        <v>-535.580368024</v>
       </c>
       <c r="Q89">
-        <v>-510.5022203760001</v>
+        <v>-518.680368024</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2985927174798543</v>
+        <v>0.3196587772698422</v>
       </c>
       <c r="T89">
-        <v>4.927400586519971</v>
+        <v>5.338017302063303</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04269289166442353</v>
+        <v>0.04220774516823691</v>
       </c>
       <c r="W89">
-        <v>0.2257330161455289</v>
+        <v>0.2258474136893298</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2587447979662032</v>
+        <v>0.2558045161711328</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9402,22 +9402,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2371047773189913</v>
+        <v>0.2390047773189913</v>
       </c>
       <c r="C90">
-        <v>-2734.504529029789</v>
+        <v>-2782.894555173548</v>
       </c>
       <c r="D90">
-        <v>696.963470970211</v>
+        <v>690.1094448264525</v>
       </c>
       <c r="E90">
-        <v>834.1680000000001</v>
+        <v>875.7040000000002</v>
       </c>
       <c r="F90">
-        <v>3655.168</v>
+        <v>3696.704</v>
       </c>
       <c r="G90">
         <v>223.7</v>
@@ -9438,37 +9438,37 @@
         <v>220.475</v>
       </c>
       <c r="M90">
-        <v>861.8886144000001</v>
+        <v>871.6828032000001</v>
       </c>
       <c r="N90">
-        <v>-641.4136144</v>
+        <v>-651.2078032000001</v>
       </c>
       <c r="O90">
-        <v>-105.833246376</v>
+        <v>-107.449287528</v>
       </c>
       <c r="P90">
-        <v>-535.580368024</v>
+        <v>-543.758515672</v>
       </c>
       <c r="Q90">
-        <v>-518.680368024</v>
+        <v>-526.8585156720001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3196587772698422</v>
+        <v>0.3445550297489187</v>
       </c>
       <c r="T90">
-        <v>5.338017302063303</v>
+        <v>5.823291602250875</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04220774516823691</v>
+        <v>0.0417335008405039</v>
       </c>
       <c r="W90">
-        <v>0.2258474136893298</v>
+        <v>0.2259592405018092</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2558045161711328</v>
+        <v>0.2529303081242661</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9484,22 +9484,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2390047773189913</v>
+        <v>0.2409047773189913</v>
       </c>
       <c r="C91">
-        <v>-2782.894555173548</v>
+        <v>-2831.151087408525</v>
       </c>
       <c r="D91">
-        <v>690.1094448264525</v>
+        <v>683.3889125914754</v>
       </c>
       <c r="E91">
-        <v>875.7040000000002</v>
+        <v>917.2400000000002</v>
       </c>
       <c r="F91">
-        <v>3696.704</v>
+        <v>3738.24</v>
       </c>
       <c r="G91">
         <v>223.7</v>
@@ -9520,37 +9520,37 @@
         <v>220.475</v>
       </c>
       <c r="M91">
-        <v>871.6828032000001</v>
+        <v>881.4769920000001</v>
       </c>
       <c r="N91">
-        <v>-651.2078032000001</v>
+        <v>-661.0019920000001</v>
       </c>
       <c r="O91">
-        <v>-107.449287528</v>
+        <v>-109.06532868</v>
       </c>
       <c r="P91">
-        <v>-543.758515672</v>
+        <v>-551.9366633200001</v>
       </c>
       <c r="Q91">
-        <v>-526.8585156720001</v>
+        <v>-535.0366633200001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3445550297489187</v>
+        <v>0.3744305327238107</v>
       </c>
       <c r="T91">
-        <v>5.823291602250875</v>
+        <v>6.405620762475964</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0417335008405039</v>
+        <v>0.04126979527560942</v>
       </c>
       <c r="W91">
-        <v>0.2259592405018092</v>
+        <v>0.2260685822740113</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2529303081242661</v>
+        <v>0.2501199713673298</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9566,22 +9566,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2409047773189913</v>
+        <v>0.2428047773189912</v>
       </c>
       <c r="C92">
-        <v>-2831.151087408525</v>
+        <v>-2879.277988155167</v>
       </c>
       <c r="D92">
-        <v>683.3889125914754</v>
+        <v>676.7980118448337</v>
       </c>
       <c r="E92">
-        <v>917.2400000000002</v>
+        <v>958.7760000000003</v>
       </c>
       <c r="F92">
-        <v>3738.24</v>
+        <v>3779.776</v>
       </c>
       <c r="G92">
         <v>223.7</v>
@@ -9602,37 +9602,37 @@
         <v>220.475</v>
       </c>
       <c r="M92">
-        <v>881.4769920000001</v>
+        <v>891.2711808000001</v>
       </c>
       <c r="N92">
-        <v>-661.0019920000001</v>
+        <v>-670.7961808000001</v>
       </c>
       <c r="O92">
-        <v>-109.06532868</v>
+        <v>-110.681369832</v>
       </c>
       <c r="P92">
-        <v>-551.9366633200001</v>
+        <v>-560.114810968</v>
       </c>
       <c r="Q92">
-        <v>-535.0366633200001</v>
+        <v>-543.2148109680001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3744305327238107</v>
+        <v>0.4109450363597896</v>
       </c>
       <c r="T92">
-        <v>6.405620762475964</v>
+        <v>7.117356402751072</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04126979527560942</v>
+        <v>0.04081628104181151</v>
       </c>
       <c r="W92">
-        <v>0.2260685822740113</v>
+        <v>0.2261755209303409</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2501199713673298</v>
+        <v>0.2473714002534031</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9648,22 +9648,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2428047773189912</v>
+        <v>0.2447047773189912</v>
       </c>
       <c r="C93">
-        <v>-2879.277988155167</v>
+        <v>-2927.278972253778</v>
       </c>
       <c r="D93">
-        <v>676.7980118448337</v>
+        <v>670.333027746222</v>
       </c>
       <c r="E93">
-        <v>958.7760000000003</v>
+        <v>1000.312</v>
       </c>
       <c r="F93">
-        <v>3779.776</v>
+        <v>3821.312</v>
       </c>
       <c r="G93">
         <v>223.7</v>
@@ -9684,37 +9684,37 @@
         <v>220.475</v>
       </c>
       <c r="M93">
-        <v>891.2711808000001</v>
+        <v>901.0653696000002</v>
       </c>
       <c r="N93">
-        <v>-670.7961808000001</v>
+        <v>-680.5903696000001</v>
       </c>
       <c r="O93">
-        <v>-110.681369832</v>
+        <v>-112.297410984</v>
       </c>
       <c r="P93">
-        <v>-560.114810968</v>
+        <v>-568.2929586160001</v>
       </c>
       <c r="Q93">
-        <v>-543.2148109680001</v>
+        <v>-551.3929586160001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4109450363597896</v>
+        <v>0.4565881659047634</v>
       </c>
       <c r="T93">
-        <v>7.117356402751072</v>
+        <v>8.007025953094956</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04081628104181151</v>
+        <v>0.04037262581309616</v>
       </c>
       <c r="W93">
-        <v>0.2261755209303409</v>
+        <v>0.2262801348332719</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2473714002534031</v>
+        <v>0.2446825806854314</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9730,22 +9730,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2447047773189912</v>
+        <v>0.2466047773189912</v>
       </c>
       <c r="C94">
-        <v>-2927.278972253778</v>
+        <v>-2975.157613946484</v>
       </c>
       <c r="D94">
-        <v>670.333027746222</v>
+        <v>663.9903860535168</v>
       </c>
       <c r="E94">
-        <v>1000.312</v>
+        <v>1041.848</v>
       </c>
       <c r="F94">
-        <v>3821.312</v>
+        <v>3862.848</v>
       </c>
       <c r="G94">
         <v>223.7</v>
@@ -9766,37 +9766,37 @@
         <v>220.475</v>
       </c>
       <c r="M94">
-        <v>901.0653696000002</v>
+        <v>910.8595584000001</v>
       </c>
       <c r="N94">
-        <v>-680.5903696000001</v>
+        <v>-690.3845584000001</v>
       </c>
       <c r="O94">
-        <v>-112.297410984</v>
+        <v>-113.913452136</v>
       </c>
       <c r="P94">
-        <v>-568.2929586160001</v>
+        <v>-576.471106264</v>
       </c>
       <c r="Q94">
-        <v>-551.3929586160001</v>
+        <v>-559.571106264</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4565881659047634</v>
+        <v>0.5152721896054439</v>
       </c>
       <c r="T94">
-        <v>8.007025953094956</v>
+        <v>9.150886803537094</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04037262581309616</v>
+        <v>0.03993851155704137</v>
       </c>
       <c r="W94">
-        <v>0.2262801348332719</v>
+        <v>0.2263824989748496</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2446825806854314</v>
+        <v>0.2420515851941901</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9812,22 +9812,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2466047773189912</v>
+        <v>0.2485047773189912</v>
       </c>
       <c r="C95">
-        <v>-2975.157613946484</v>
+        <v>-3022.917353466527</v>
       </c>
       <c r="D95">
-        <v>663.9903860535168</v>
+        <v>657.7666465334737</v>
       </c>
       <c r="E95">
-        <v>1041.848</v>
+        <v>1083.384</v>
       </c>
       <c r="F95">
-        <v>3862.848</v>
+        <v>3904.384</v>
       </c>
       <c r="G95">
         <v>223.7</v>
@@ -9848,37 +9848,37 @@
         <v>220.475</v>
       </c>
       <c r="M95">
-        <v>910.8595584000001</v>
+        <v>920.6537472000001</v>
       </c>
       <c r="N95">
-        <v>-690.3845584000001</v>
+        <v>-700.1787472000001</v>
       </c>
       <c r="O95">
-        <v>-113.913452136</v>
+        <v>-115.529493288</v>
       </c>
       <c r="P95">
-        <v>-576.471106264</v>
+        <v>-584.6492539120001</v>
       </c>
       <c r="Q95">
-        <v>-559.571106264</v>
+        <v>-567.7492539120001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5152721896054439</v>
+        <v>0.5935175545396848</v>
       </c>
       <c r="T95">
-        <v>9.150886803537094</v>
+        <v>10.67603460412661</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03993851155704137</v>
+        <v>0.03951363377451965</v>
       </c>
       <c r="W95">
-        <v>0.2263824989748496</v>
+        <v>0.2264826851559683</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2420515851941901</v>
+        <v>0.2394765683304222</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9894,22 +9894,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2485047773189912</v>
+        <v>0.2504047773189912</v>
       </c>
       <c r="C96">
-        <v>-3022.917353466527</v>
+        <v>-3070.561503260435</v>
       </c>
       <c r="D96">
-        <v>657.7666465334737</v>
+        <v>651.6584967395657</v>
       </c>
       <c r="E96">
-        <v>1083.384</v>
+        <v>1124.920000000001</v>
       </c>
       <c r="F96">
-        <v>3904.384</v>
+        <v>3945.920000000001</v>
       </c>
       <c r="G96">
         <v>223.7</v>
@@ -9930,37 +9930,37 @@
         <v>220.475</v>
       </c>
       <c r="M96">
-        <v>920.6537472000001</v>
+        <v>930.4479360000001</v>
       </c>
       <c r="N96">
-        <v>-700.1787472000001</v>
+        <v>-709.9729360000001</v>
       </c>
       <c r="O96">
-        <v>-115.529493288</v>
+        <v>-117.14553444</v>
       </c>
       <c r="P96">
-        <v>-584.6492539120001</v>
+        <v>-592.8274015600001</v>
       </c>
       <c r="Q96">
-        <v>-567.7492539120001</v>
+        <v>-575.9274015600001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5935175545396848</v>
+        <v>0.7030610654476219</v>
       </c>
       <c r="T96">
-        <v>10.67603460412661</v>
+        <v>12.81124152495194</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03951363377451965</v>
+        <v>0.03909770078741944</v>
       </c>
       <c r="W96">
-        <v>0.2264826851559683</v>
+        <v>0.2265807621543265</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2394765683304222</v>
+        <v>0.2369557623479966</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9976,22 +9976,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2504047773189912</v>
+        <v>0.2523047773189913</v>
       </c>
       <c r="C97">
-        <v>-3070.561503260435</v>
+        <v>-3118.093253866691</v>
       </c>
       <c r="D97">
-        <v>651.6584967395657</v>
+        <v>645.6627461333095</v>
       </c>
       <c r="E97">
-        <v>1124.920000000001</v>
+        <v>1166.456000000001</v>
       </c>
       <c r="F97">
-        <v>3945.920000000001</v>
+        <v>3987.456000000001</v>
       </c>
       <c r="G97">
         <v>223.7</v>
@@ -10012,37 +10012,37 @@
         <v>220.475</v>
       </c>
       <c r="M97">
-        <v>930.4479360000001</v>
+        <v>940.2421248000002</v>
       </c>
       <c r="N97">
-        <v>-709.9729360000001</v>
+        <v>-719.7671248000001</v>
       </c>
       <c r="O97">
-        <v>-117.14553444</v>
+        <v>-118.761575592</v>
       </c>
       <c r="P97">
-        <v>-592.8274015600001</v>
+        <v>-601.0055492080002</v>
       </c>
       <c r="Q97">
-        <v>-575.9274015600001</v>
+        <v>-584.1055492080002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7030610654476219</v>
+        <v>0.8673763318095278</v>
       </c>
       <c r="T97">
-        <v>12.81124152495194</v>
+        <v>16.01405190618993</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03909770078741944</v>
+        <v>0.03869043307088382</v>
       </c>
       <c r="W97">
-        <v>0.2265807621543265</v>
+        <v>0.2266767958818856</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2369557623479966</v>
+        <v>0.2344874731568717</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -10058,22 +10058,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2523047773189912</v>
+        <v>0.2542047773189913</v>
       </c>
       <c r="C98">
-        <v>-3118.093253866691</v>
+        <v>-3165.515679472835</v>
       </c>
       <c r="D98">
-        <v>645.6627461333095</v>
+        <v>639.7763205271649</v>
       </c>
       <c r="E98">
-        <v>1166.456</v>
+        <v>1207.992</v>
       </c>
       <c r="F98">
-        <v>3987.456</v>
+        <v>4028.992</v>
       </c>
       <c r="G98">
         <v>223.7</v>
@@ -10094,37 +10094,37 @@
         <v>220.475</v>
       </c>
       <c r="M98">
-        <v>940.2421248000001</v>
+        <v>950.0363136000001</v>
       </c>
       <c r="N98">
-        <v>-719.7671248</v>
+        <v>-729.5613136000001</v>
       </c>
       <c r="O98">
-        <v>-118.761575592</v>
+        <v>-120.377616744</v>
       </c>
       <c r="P98">
-        <v>-601.005549208</v>
+        <v>-609.1836968560001</v>
       </c>
       <c r="Q98">
-        <v>-584.1055492080001</v>
+        <v>-592.2836968560001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8673763318095256</v>
+        <v>1.141235109079368</v>
       </c>
       <c r="T98">
-        <v>16.01405190618989</v>
+        <v>21.35206920825319</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03869043307088382</v>
+        <v>0.0382915626268541</v>
       </c>
       <c r="W98">
-        <v>0.2266767958818856</v>
+        <v>0.2267708495325878</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2344874731568717</v>
+        <v>0.2320700765263884</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -10140,22 +10140,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2542047773189913</v>
+        <v>0.2561047773189912</v>
       </c>
       <c r="C99">
-        <v>-3165.515679472835</v>
+        <v>-3212.83174317133</v>
       </c>
       <c r="D99">
-        <v>639.7763205271649</v>
+        <v>633.9962568286702</v>
       </c>
       <c r="E99">
-        <v>1207.992</v>
+        <v>1249.528</v>
       </c>
       <c r="F99">
-        <v>4028.992</v>
+        <v>4070.528</v>
       </c>
       <c r="G99">
         <v>223.7</v>
@@ -10176,37 +10176,37 @@
         <v>220.475</v>
       </c>
       <c r="M99">
-        <v>950.0363136000001</v>
+        <v>959.8305024000001</v>
       </c>
       <c r="N99">
-        <v>-729.5613136000001</v>
+        <v>-739.3555024000001</v>
       </c>
       <c r="O99">
-        <v>-120.377616744</v>
+        <v>-121.993657896</v>
       </c>
       <c r="P99">
-        <v>-609.1836968560001</v>
+        <v>-617.361844504</v>
       </c>
       <c r="Q99">
-        <v>-592.2836968560001</v>
+        <v>-600.4618445040001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.141235109079368</v>
+        <v>1.688952663619051</v>
       </c>
       <c r="T99">
-        <v>21.35206920825319</v>
+        <v>32.02810381237978</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0382915626268541</v>
+        <v>0.03790083239596783</v>
       </c>
       <c r="W99">
-        <v>0.2267708495325878</v>
+        <v>0.2268629837210308</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2320700765263884</v>
+        <v>0.2297020145210171</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -10222,22 +10222,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2561047773189912</v>
+        <v>0.2580047773189912</v>
       </c>
       <c r="C100">
-        <v>-3212.83174317133</v>
+        <v>-3260.044301933076</v>
       </c>
       <c r="D100">
-        <v>633.9962568286702</v>
+        <v>628.3196980669243</v>
       </c>
       <c r="E100">
-        <v>1249.528</v>
+        <v>1291.064</v>
       </c>
       <c r="F100">
-        <v>4070.528</v>
+        <v>4112.064</v>
       </c>
       <c r="G100">
         <v>223.7</v>
@@ -10258,37 +10258,37 @@
         <v>220.475</v>
       </c>
       <c r="M100">
-        <v>959.8305024000001</v>
+        <v>969.6246912000001</v>
       </c>
       <c r="N100">
-        <v>-739.3555024000001</v>
+        <v>-749.1496912000001</v>
       </c>
       <c r="O100">
-        <v>-121.993657896</v>
+        <v>-123.609699048</v>
       </c>
       <c r="P100">
-        <v>-617.361844504</v>
+        <v>-625.5399921520001</v>
       </c>
       <c r="Q100">
-        <v>-600.4618445040001</v>
+        <v>-608.6399921520001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.688952663619051</v>
+        <v>3.332105327238102</v>
       </c>
       <c r="T100">
-        <v>32.02810381237978</v>
+        <v>64.05620762475957</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03790083239596783</v>
+        <v>0.03751799570509946</v>
       </c>
       <c r="W100">
-        <v>0.2268629837210308</v>
+        <v>0.2269532566127375</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -10296,91 +10296,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2297020145210171</v>
+        <v>0.227381792152118</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2580047773189912</v>
-      </c>
-      <c r="C101">
-        <v>-3260.044301933076</v>
-      </c>
-      <c r="D101">
-        <v>628.3196980669243</v>
-      </c>
-      <c r="E101">
-        <v>1291.064</v>
-      </c>
-      <c r="F101">
-        <v>4112.064</v>
-      </c>
-      <c r="G101">
-        <v>223.7</v>
-      </c>
-      <c r="H101">
-        <v>1332.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>237.375</v>
-      </c>
-      <c r="K101">
-        <v>16.90000000000001</v>
-      </c>
-      <c r="L101">
-        <v>220.475</v>
-      </c>
-      <c r="M101">
-        <v>969.6246912000001</v>
-      </c>
-      <c r="N101">
-        <v>-749.1496912000001</v>
-      </c>
-      <c r="O101">
-        <v>-123.609699048</v>
-      </c>
-      <c r="P101">
-        <v>-625.5399921520001</v>
-      </c>
-      <c r="Q101">
-        <v>-608.6399921520001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.332105327238102</v>
-      </c>
-      <c r="T101">
-        <v>64.05620762475957</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03751799570509946</v>
-      </c>
-      <c r="W101">
-        <v>0.2269532566127375</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.227381792152118</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
